--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,16 +497,11 @@
           <t>AEO and GEO Marketing Manager</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/aeo-and-geo-marketing-manager/7844214</t>
@@ -517,7 +512,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -535,16 +529,11 @@
           <t>AI Product Manager, Professional Services</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/ai-product-manager-professional-services/8064526</t>
@@ -555,7 +544,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,16 +561,11 @@
           <t>AV Events Manager</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/av-events-manager/8078126</t>
@@ -593,7 +576,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,16 +593,11 @@
           <t>Account Executive - Enterprise, Grower</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
@@ -631,7 +608,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,16 +625,11 @@
           <t>Account Executive - Enterprise, Growth</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
@@ -669,7 +640,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -687,16 +657,11 @@
           <t>Account Executive - Startups, Hunter ANZ</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-startups-hunter-anz/8040874</t>
@@ -707,7 +672,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -725,16 +689,11 @@
           <t>Account Executive, AI Sales (Grower)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-ai-sales-grower/7954688</t>
@@ -745,7 +704,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -763,16 +721,11 @@
           <t>Account Executive, Bridge</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-bridge/8077887</t>
@@ -783,7 +736,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -801,16 +753,11 @@
           <t>Account Executive, Bridge</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-bridge/8023928</t>
@@ -821,7 +768,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -839,16 +785,11 @@
           <t>Account Executive, Commercial Grower (Japanese Fluency)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
@@ -859,7 +800,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,16 +817,11 @@
           <t>Account Executive, Commercial Hunter (Japanese Fluency)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
@@ -897,7 +832,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -915,16 +849,11 @@
           <t>Account Executive, Cross Border China</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
@@ -935,7 +864,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -953,16 +881,11 @@
           <t>Managed Payments</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>https://stripe.com/managed-payments</t>
@@ -973,7 +896,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -991,16 +913,11 @@
           <t>Payment links</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>https://stripe.com/payments/payment-links</t>
@@ -1011,7 +928,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1029,16 +945,11 @@
           <t>Payment methods</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>https://stripe.com/payments/payment-methods</t>
@@ -1049,7 +960,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1067,16 +977,11 @@
           <t>Payments</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>https://stripe.com/payments</t>
@@ -1087,7 +992,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1105,16 +1009,11 @@
           <t>Global businesses</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>https://stripe.com/use-cases/global-businesses</t>
@@ -1125,7 +1024,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1143,16 +1041,11 @@
           <t>In-app payments</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>https://stripe.com/use-cases/in-app-payments</t>
@@ -1163,7 +1056,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1181,16 +1073,11 @@
           <t>Customer stories</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>https://stripe.com/customers</t>
@@ -1201,7 +1088,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1219,16 +1105,11 @@
           <t>Prohibited and restricted businesses</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>https://stripe.com/legal/restricted-businesses</t>
@@ -1239,7 +1120,6 @@
           <t>https://stripe.com/jobs/search</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1257,16 +1137,11 @@
           <t>Backend Engineer, Payments and Risk</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/backend-engineer-payments-and-risk-at-stripe-4439350439?refId=bXgz36nREUnjoMipWlUSPw%3D%3D&amp;trackingId=u%2F93zYLJmJYKQcpcVKXA7w%3D%3D</t>
@@ -1277,7 +1152,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1295,16 +1169,11 @@
           <t>Data Scientist, Payments</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/data-scientist-payments-at-stripe-4430974251?refId=bXgz36nREUnjoMipWlUSPw%3D%3D&amp;trackingId=0QZ%2B8UlWv7hhzxIxZ2PZyQ%3D%3D</t>
@@ -1315,7 +1184,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1333,16 +1201,11 @@
           <t>Account Executive, Enterprise - Hunter</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-hunter-at-stripe-4430731526?refId=bXgz36nREUnjoMipWlUSPw%3D%3D&amp;trackingId=wcXVfhSQnjJkbRcTiFYAHA%3D%3D</t>
@@ -1353,7 +1216,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1371,16 +1233,11 @@
           <t>Staff Product Manager, Issuing</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/staff-product-manager-issuing-at-stripe-4439344711?refId=bXgz36nREUnjoMipWlUSPw%3D%3D&amp;trackingId=Rc9TePTRpoOKe%2Fd0r4ommw%3D%3D</t>
@@ -1391,7 +1248,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1409,16 +1265,11 @@
           <t>Tax Technology Lead</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/tax-technology-lead-at-stripe-4430728690?refId=bXgz36nREUnjoMipWlUSPw%3D%3D&amp;trackingId=zgFXlLBNe7E0r8OFjWz3ow%3D%3D</t>
@@ -1429,7 +1280,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1447,16 +1297,11 @@
           <t>Manager jobs1,880,925 open jobs</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -1467,7 +1312,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1485,16 +1329,11 @@
           <t>Account Executive jobs71,457 open jobs</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest-browse_jobs</t>
@@ -1505,7 +1344,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1523,16 +1361,11 @@
           <t>Director jobs1,220,357 open jobs</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/director-jobs?trk=organization_guest-browse_jobs</t>
@@ -1543,7 +1376,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1561,16 +1393,11 @@
           <t>Marketing Manager jobs106,879 open jobs</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/marketing-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -1581,7 +1408,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1599,16 +1425,11 @@
           <t>Project Manager jobs253,048 open jobs</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/project-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -1619,7 +1440,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1637,16 +1457,11 @@
           <t>Account Manager jobs121,519 open jobs</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -1657,7 +1472,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1675,16 +1489,11 @@
           <t>Product Manager jobs199,941 open jobs</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/product-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -1695,7 +1504,6 @@
           <t>https://www.linkedin.com/company/stripe/jobs/</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1713,16 +1521,11 @@
           <t>More info commercial careers</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>https://careers.adyen.com/career-types/commercial</t>
@@ -1733,7 +1536,6 @@
           <t>https://careers.adyen.com/</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1751,16 +1553,11 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>https://careers.adyen.com/career-types/commercial</t>
@@ -1771,7 +1568,6 @@
           <t>https://careers.adyen.com/</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1789,16 +1585,11 @@
           <t>Payment Partnerships Lead</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=c9%2BYkEfMBcXk5aJFolmeiA%3D%3D&amp;trackingId=wegRAIrDD8YDLpS7X1CQlw%3D%3D</t>
@@ -1809,7 +1600,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1827,16 +1617,11 @@
           <t>Product Marketing Manager</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/jobs/view/product-marketing-manager-at-adyen-4438341758?refId=c9%2BYkEfMBcXk5aJFolmeiA%3D%3D&amp;trackingId=nmgOVjYlLioNl3ydSz1J1A%3D%3D</t>
@@ -1847,7 +1632,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1865,16 +1649,11 @@
           <t>Senior Communication Business Partner - Tech</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/senior-communication-business-partner-tech-at-adyen-4326302346?refId=c9%2BYkEfMBcXk5aJFolmeiA%3D%3D&amp;trackingId=ZdK4eRyuyXJDiwj5TaTK9Q%3D%3D</t>
@@ -1885,7 +1664,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1903,16 +1681,11 @@
           <t>Senior Manager, Community Marketing</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/senior-manager-community-marketing-at-adyen-4429350787?refId=c9%2BYkEfMBcXk5aJFolmeiA%3D%3D&amp;trackingId=yIPj2db%2BlykuFHC5KzjR3A%3D%3D</t>
@@ -1923,7 +1696,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1941,16 +1713,11 @@
           <t>Team Lead, Project Operations Management</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/team-lead-project-operations-management-at-adyen-4419306318?refId=c9%2BYkEfMBcXk5aJFolmeiA%3D%3D&amp;trackingId=xnUCDoLizALTLs%2F99RMEtQ%3D%3D</t>
@@ -1961,7 +1728,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1979,16 +1745,11 @@
           <t>Senior Product Manager - Split Payments</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/jobs/view/senior-product-manager-split-payments-at-adyen-4438305258?refId=c9%2BYkEfMBcXk5aJFolmeiA%3D%3D&amp;trackingId=bf0qUB19Ab2uQ62LS8ckWg%3D%3D</t>
@@ -1999,7 +1760,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2017,16 +1777,11 @@
           <t>Manager jobs1,880,925 open jobs</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -2037,7 +1792,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2055,16 +1809,11 @@
           <t>Account Manager jobs121,519 open jobs</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -2075,7 +1824,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2093,16 +1841,11 @@
           <t>Marketing Manager jobs106,879 open jobs</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/marketing-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -2113,7 +1856,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2131,16 +1873,11 @@
           <t>Project Manager jobs253,048 open jobs</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/project-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -2151,7 +1888,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2169,16 +1905,11 @@
           <t>Director jobs1,220,357 open jobs</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/director-jobs?trk=organization_guest-browse_jobs</t>
@@ -2189,7 +1920,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2207,16 +1937,11 @@
           <t>Account Executive jobs71,457 open jobs</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest-browse_jobs</t>
@@ -2227,7 +1952,6 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2245,16 +1969,11 @@
           <t>Product Manager jobs199,941 open jobs</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/product-manager-jobs?trk=organization_guest-browse_jobs</t>
@@ -2265,7 +1984,462 @@
           <t>https://www.linkedin.com/company/adyen/jobs/</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Backend Engineer, Payments and Risk</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/backend-engineer-payments-and-risk-at-stripe-4439350439?refId=kqlqTIeYN%2FHEXJLvYZOiWw%3D%3D&amp;trackingId=jono%2BkhsA9VKO%2BYc7o9a2Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Data Scientist, Payments</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/jobs/view/data-scientist-payments-at-stripe-4430974251?refId=kqlqTIeYN%2FHEXJLvYZOiWw%3D%3D&amp;trackingId=ayHLbfk5i9plA3Se43A0kw%3D%3D</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Account Executive, Enterprise - Hunter</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-hunter-at-stripe-4430731526?refId=kqlqTIeYN%2FHEXJLvYZOiWw%3D%3D&amp;trackingId=osjJ4SUurAtR02ncbMB1Ag%3D%3D</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, Issuing</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/staff-product-manager-issuing-at-stripe-4439344711?refId=kqlqTIeYN%2FHEXJLvYZOiWw%3D%3D&amp;trackingId=AEfQmldWokzCeoPDy5BISA%3D%3D</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tax Technology Lead</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/tax-technology-lead-at-stripe-4430728690?refId=kqlqTIeYN%2FHEXJLvYZOiWw%3D%3D&amp;trackingId=f%2F6yCgsn0aqgkQDgmRVd9w%3D%3D</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Product Manager, Link - Consumer</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/product-manager-link-consumer-at-stripe-4430121352?refId=kqlqTIeYN%2FHEXJLvYZOiWw%3D%3D&amp;trackingId=ckN%2B9acrgyIFfZbqSDerdQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Payment Partnerships Lead</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=A4HB5hpSLdsbSc81MsCMjA%3D%3D&amp;trackingId=d6Pkl98I%2BW%2FHm3VoafhsOw%3D%3D</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/product-marketing-manager-at-adyen-4438341758?refId=A4HB5hpSLdsbSc81MsCMjA%3D%3D&amp;trackingId=xoobNvLu36hZG7LEPeEytg%3D%3D</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Senior Communication Business Partner - Tech</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-communication-business-partner-tech-at-adyen-4326302346?refId=A4HB5hpSLdsbSc81MsCMjA%3D%3D&amp;trackingId=6R2j0LrKrOyWMvqPK6P3FQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Senior Manager, Community Marketing</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-community-marketing-at-adyen-4429350787?refId=A4HB5hpSLdsbSc81MsCMjA%3D%3D&amp;trackingId=a5iKao1OG%2BG7OBfiZnU9nw%3D%3D</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Team Lead, Project Operations Management</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/team-lead-project-operations-management-at-adyen-4419306318?refId=A4HB5hpSLdsbSc81MsCMjA%3D%3D&amp;trackingId=vzQBEevShQ4MoSr2v6otuw%3D%3D</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>JOB-20260801-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Split Payments</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/senior-product-manager-split-payments-at-adyen-4438305258?refId=A4HB5hpSLdsbSc81MsCMjA%3D%3D&amp;trackingId=rTRAz%2BIB4iK7Japo0xWXng%3D%3D</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2902,7 +3076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,6 +3145,35 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:48:56</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Visa(Career:('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer')))</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2987,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3162,6 +3365,146 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:48:56</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:48:56</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stripe/jobs/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:48:56</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://careers.adyen.com/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:48:56</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adyen/jobs/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:48:56</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1880,6 +1880,2351 @@
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>45</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=ZlEurwVGnTVA%2FM43oEI%2F0A%3D%3D&amp;trackingId=lS48JaPBbUQvx3vwvEL9Yg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Account Executive, Enterprise Platforms, Tier 2 Grower</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-platforms-tier-2-grower-at-stripe-4439345642?refId=ZlEurwVGnTVA%2FM43oEI%2F0A%3D%3D&amp;trackingId=rpqxl1mrtZ7B3gWewGPGyQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Payment Partnerships Lead</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>75</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=z6prmF151YCLJu%2Bpqgk4Ww%3D%3D&amp;trackingId=J%2F76bvAFbwwck3WTMjUfBg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Manager, Customer Success</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>35</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/jobs/view/manager-customer-success-at-mastercard-4436642003?refId=9SDvwT9yaGM4TK%2FqdNUjCQ%3D%3D&amp;trackingId=uwQZsl1zsaTh6AfQO1ap0Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Regional Customer Success Operations Manager</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>55</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/regional-customer-success-operations-manager-at-payoneer-4447800339?refId=AutuwIKZj5vumDHFbEyehw%3D%3D&amp;trackingId=hivD4CTwN42k75G2rrqYMQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Account Executive, Startups (AI Solutions)StartupsStartups•SeoulAPAC,SeoulSeoul</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>55</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b05c397a-d608-4684-aab9-ac65a10f8dce/account-executive-startups-ai-solutions/</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•BeijingAPAC,BeijingBeijing</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>30</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>30</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/9a87615c-17d7-4b94-b2ad-fb1e72c74e74/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sales Executive, Enterprise AccountsSalesAPAC, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>25</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/7f1f3577-001f-45f0-bfa4-1fde10a00156/sales-executive-enterprise-accounts/</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AustraliaChinaCorporate AffairsDesignEngineeringExecutiveFinance and Corporate DevelopmentFinancial PartnershipsFranceGlobalHong KongIsraelJapanLegal, Risk and ComplianceLithuaniaLocationsMalaysiaMarketingNetherlandsPeople and TalentProductPurpose &amp; impactSalesSingaporeStrategic PartnershipsStrategy and OperationsTeamsUncategorizedUnited Arab EmiratesUnited KingdomUnited StatesPurpose &amp; impactAirwallex Funding 2026: $11B Valuation Fuels Global Fintech GrowthAt Airwallex, we’re on a rare trajectory. Today we shared that our Series F funding, bringing Airwallex’s total raised to $1.2 billion, with a valuation of $6.2 billion. In March 2025, we surpassed $720M in annualized revenue—a 90% year-over-year increase—highlighting our momentum and vision. Few fintechs achieve this scale and pace, and we believe this is only the beginning.Airwallex Careers25 June 20264 min</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>30</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GlobalPioneering WorkPioneering WorkWhy the Airwallex Solutions Team Sits in Product &amp; EngineeringAt most companies, Solutions lives in Sales. At Airwallex, our Solutions team sits inside Product &amp; Engineering. Learn how our architects and engineers solve for the customer in front of us while building scalable products for the customers we haven't met yet.Michael Eshoo09 June 20263 min</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>40</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Account Executive/Senior Account Executive, Enterprise</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>40</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/account-executive-senior-account-executive-enterprise-at-airwallex-4354110015?refId=Yym4eUAqrctz7s2eLZDxtg%3D%3D&amp;trackingId=WGSef%2FHMLUZyeqGT5B0TZQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Money Transfer OperatorsExpand your operations seamlessly around the world with payment corridor support for 190+ countries</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>25</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MarketplacesAccelerate business growth with white-label payout solutions for global marketplace platforms</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>45</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AirlinesStreamline operations and lower cost with closed-loop payment solutions</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>60</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Money Transfer OperatorsExpand your operations seamlessly around the world with payment corridor support for 190+ countries</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>25</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MarketplacesAccelerate business growth with white-label payout solutions for global marketplace platforms</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>45</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AirlinesStreamline operations and lower cost with closed-loop payment solutions</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Payments LinksAccept payments on any channel</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>45</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Pay-insOmnichannel payment solutions</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>75</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Online retailEcommerce payment solutions</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>40</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Financial servicesPayment solutions for finance</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>40</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GovernmentPublic sector payment solutions</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>40</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Small &amp; medium sized businessesSMB tailored payment solutions</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>45</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Canada bank transfer|Nuveinuvei.com/solutions/canada-bank-transferUnlock seamless financial transactions with Interac and Instant Bank Transfer. Enjoy rapid, secure payments anytime, anywhere.</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>45</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>UK bank transfer|Nuveinuvei.com/solutions/uk-bank-transferUnlock seamless financial transactions with Faster Payments and Pay with Bank Transfer. Enjoy rapid, secure payments anytime, anywhere.</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>45</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EU bank transfer|Nuveinuvei.com/solutions/eu-bank-transferUnlock seamless financial transactions with SEPA and SEPA Instant Credit Transfer. Enjoy rapid, secure payments anytime, anywhere.</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>45</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>U.S. bank transfer|Nuveinuvei.com/solutions/us-bank-transferDiscover Nuvei's U.S. Bank Transfer services for seamless, rapid, and secure payments. Leverage ACH, RTP, and FedNow networks for flexible money transfers.</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>45</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Issuing|Nuveinuvei.com/solutions/issuingDiscover Nuvei's seamless issuing payment solutions, including customizable physical and virtual cards, unified acquiring and issuing, and data-driven insights.</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>85</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>APM|Nuveinuvei.com/solutions/apmPower your checkout with APM solutions: digital wallets, local bank transfers, QR payments, buy-now-pay-later, and more. Deliver seamless, regionally preferred payment experiences that boost conversions and expand your reach.</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>55</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Real-time payments|Nuveinuvei.com/solutions/real-time-paymentsBoost your business with Nuvei's real-time payments. Experience seamless, instant transaction processing to enhance cash flow and stay compliant with secure payment solutions.</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>50</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bank transfers|Nuveinuvei.com/solutions/bank-transfersExperience cost-efficient, reliable, and fast bank transfers with Nuvei. Streamline your payment processing, elevate customer satisfaction, and boost conversion rates globally.</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>40</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Reconciliation management|Nuveinuvei.com/solutions/reconciliation-managementStreamline your financial processes with Nuvei's Reconciliation Management. Automate and manage payment reconciliation effortlessly for improved accuracy and efficiency.</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>40</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Payment orchestration|Nuveinuvei.com/solutions/payment-orchestrationMaster your payment operations with Nuvei's Payment Orchestration. Streamline and manage complex payment flows with our comprehensive tools for maximum control and insight.</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>60</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Crypto &amp; digital assets|Nuveinuvei.com/solutions/crypto-digital-assetsStreamline your Web3 business with Nuvei's painless fiat-crypto conversion. Partner with us for seamless blockchain payment technologies and infrastructure to drive your crypto success.</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Currency management|Nuveinuvei.com/solutions/currency-managementFacilitate global commerce with Nuvei's Currency Management. Simplify FX transactions, enhance payment flexibility, and offer customers native currency options for improved satisfaction.</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>40</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fraud &amp; risk management|Nuveinuvei.com/solutions/fraud-risk-managementProtect your business with Nuvei's Fraud &amp; Risk Management solutions. Minimize threats and secure data while maintaining a smooth customer experience.</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>40</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Authorization optimization|Nuveinuvei.com/solutions/authorization-optimizationOptimize payment authorizations across every channel. Boost your approval rates by up to 5 points, reduce declines, and recover revenue with intelligent routing and retry.</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>75</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Healthcare payment solutions|Nuveinuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>40</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hospitality|Nuveinuvei.com/use-cases/hospitalityNuvei offers tailored payment solutions for hospitality businesses, streamlining transactions for an elevated customer experience. Discover how our flexible, secure and easy-to-use systems can enhance your venue’s payment flow.</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>45</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Automotive|Nuveinuvei.com/use-cases/automotiveBoost customer satisfaction and operational efficiency with Nuvei's tailored automotive payment solutions. Enjoy seamless DMS integrations, multiple payment options, advanced fraud protection, and 24/7 support to elevate your business and focus on delivering exceptional service.</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>45</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Grocery|Nuveinuvei.com/use-cases/grocerySimplify and elevate your grocery operations with Nuvei’s integrated payment solutions. Deliver fast, secure, and flexible payment experiences that build customer loyalty and keep your business thriving.</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>65</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Crypto platforms &amp; exchanges|Nuveinuvei.com/use-cases/crypto-platforms-exchangesDiscover the future of cryptocurrency transactions with Nuvei's scalable blockchain solutions. Access global payment ecosystems, enjoy seamless fiat-to-crypto exchanges, and benefit from full fraud protection. Ideal for platforms and exchanges seeking efficiency, compliance, and extended market reach.</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>40</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Small &amp; medium sized businesses|Nuveinuvei.com/use-cases/small-medium-sized-businessesEmpower your SMB with Nuvei's tailored payment solutions. Enjoy flexible, secure payment processing, innovative POS hardware, and 24/7 support to enhance your customer experience and growth.</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>50</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Government payments|Nuveinuvei.com/use-cases/governmentNuvei offers a comprehensive government payment solution designed for public sector agencies. Streamline operations, enhance security, reduce costs, and improve citizen experience with our innovative payment technology.</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>30</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Business to business|Nuveinuvei.com/use-cases/business-to-businessDiscover leading B2B payment solutions that enhance efficiency. Elevate your AP and AR business operations today for seamless financial management.</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>65</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Financial services|Nuveinuvei.com/use-cases/financial-servicesTransform your financial services with Nuvei's cutting-edge payment solutions. Experience enhanced security, compliance, and efficiency. Discover how we can help streamline your operations and elevate customer trust.</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>60</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Online gaming|Nuveinuvei.com/use-cases/online-gamingUnlock the full potential of your gaming platform with Nuvei's specialized payment solutions for the Online Gaming industry. Ensure seamless, secure transactions and enhance player satisfaction.</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>40</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Digital content &amp; subscriptions|Nuveinuvei.com/use-cases/digital-content-subscriptionsEnhance digital content revenue with Nuvei's payment solutions. Perfect for subscriptions, offering seamless billing, global market access, and secure transaction processing.</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>45</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nuvei Completes First-Party In-Agent Payment with Visa; Unveils Merchant-Led Agentic Payments Strategy|Nuveinuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategyFirst live in-agent purchase authorized across multiple issuers on Visa railsFirst live in-agent purchase authorized across multiple issuers on Visa rails</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Nuvei to Acquire Payoneer for $2.75 Billion, Creating a Leading Global Platform for Local and Cross-Border Commerce|Nuveinuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerceNuvei is acquiring Payoneer for $2.75 billion. ‍The combined company will give businesses a single partner to accept, hold, and move money – including stablecoin transactions – across 190+ countries and territories.At close, the combined company is expected to generate approximately $3 billion in annual revenue and process more than $500 billion in annual payment volume for more than 2.4 million customers</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>55</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Syspro and Nuvei partner to embed integrated payments into ERP for manufacturing and distribution|Nuveinuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distributionPartnership modernizes payment operations for underserved sectors, enabling businesses to collect funds faster, operate with greater control, and scale across marketsPartnership modernizes payment operations for underserved sectors, enabling businesses to collect funds faster, operate with greater control, and scale across markets</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>45</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>What global expansion keeps getting wrong about payments|Nuveinuvei.com/posts/the-last-percentage-point-what-global-expansion-keeps-getting-wrong-about-paymentsGlobal expansion fails at checkout more often than strategy. Learn why payment methods, local acquiring, and approval rates should be your first decision, not your last.</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>50</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/the-last-percentage-point-what-global-expansion-keeps-getting-wrong-about-payments</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>40</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446785559?refId=j%2BX8959nDpyoRBBT8Bvq8A%3D%3D&amp;trackingId=hcv3ZqzaQUBnM%2BcgthmjsQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>40</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446755868?refId=j%2BX8959nDpyoRBBT8Bvq8A%3D%3D&amp;trackingId=cesN19ze1%2F0R47R3G%2FyYgQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>40</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-mexico-at-nuvei-4436810355?refId=j%2BX8959nDpyoRBBT8Bvq8A%3D%3D&amp;trackingId=sdPv4v9TCcsdta8hY2geRQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Business Solutions Director, Payments</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>50</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4447000136?refId=q6bRKe1hf4IEYvdkC0tbxg%3D%3D&amp;trackingId=%2F8kGafkJTA5b2PoQEUCUvw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Customer Success &amp; Enterprise Support Lead, APAC</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>55</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/customer-success-enterprise-support-lead-apac-at-perplexity-4420517260?refId=GjqpgE5IyQvxESifRJeFvQ%3D%3D&amp;trackingId=gbThuX17q6mD71gQunt5XQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager, Banks</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>40</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager, Banks</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>40</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Payment Operations Regional Product Specialist</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>25</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Payment Operations</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>25</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Payment Operations</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>25</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager, Banks</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>40</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Payment Operations</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>25</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Payment Operations</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>25</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Business Development</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>40</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -2525,7 +4870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2591,8 +4936,35 @@
       <c r="F2" t="n">
         <v>15</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2609,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3924,6 +6296,2938 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-ai-sales-grower/7954688</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=ZlEurwVGnTVA%2FM43oEI%2F0A%3D%3D&amp;trackingId=lS48JaPBbUQvx3vwvEL9Yg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-platforms-tier-2-grower-at-stripe-4439345642?refId=ZlEurwVGnTVA%2FM43oEI%2F0A%3D%3D&amp;trackingId=rpqxl1mrtZ7B3gWewGPGyQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=z6prmF151YCLJu%2Bpqgk4Ww%3D%3D&amp;trackingId=J%2F76bvAFbwwck3WTMjUfBg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/jobs/view/manager-customer-success-at-mastercard-4436642003?refId=9SDvwT9yaGM4TK%2FqdNUjCQ%3D%3D&amp;trackingId=uwQZsl1zsaTh6AfQO1ap0Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/regional-customer-success-operations-manager-at-payoneer-4447800339?refId=AutuwIKZj5vumDHFbEyehw%3D%3D&amp;trackingId=hivD4CTwN42k75G2rrqYMQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b05c397a-d608-4684-aab9-ac65a10f8dce/account-executive-startups-ai-solutions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/9a87615c-17d7-4b94-b2ad-fb1e72c74e74/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/7f1f3577-001f-45f0-bfa4-1fde10a00156/sales-executive-enterprise-accounts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/account-executive-senior-account-executive-enterprise-at-airwallex-4354110015?refId=Yym4eUAqrctz7s2eLZDxtg%3D%3D&amp;trackingId=WGSef%2FHMLUZyeqGT5B0TZQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/the-last-percentage-point-what-global-expansion-keeps-getting-wrong-about-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446785559?refId=j%2BX8959nDpyoRBBT8Bvq8A%3D%3D&amp;trackingId=hcv3ZqzaQUBnM%2BcgthmjsQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446755868?refId=j%2BX8959nDpyoRBBT8Bvq8A%3D%3D&amp;trackingId=cesN19ze1%2F0R47R3G%2FyYgQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-mexico-at-nuvei-4436810355?refId=j%2BX8959nDpyoRBBT8Bvq8A%3D%3D&amp;trackingId=sdPv4v9TCcsdta8hY2geRQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4453463006</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4447000136?refId=q6bRKe1hf4IEYvdkC0tbxg%3D%3D&amp;trackingId=%2F8kGafkJTA5b2PoQEUCUvw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/customer-success-enterprise-support-lead-apac-at-perplexity-4420517260?refId=GjqpgE5IyQvxESifRJeFvQ%3D%3D&amp;trackingId=gbThuX17q6mD71gQunt5XQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ripple/jobs/</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/ripple/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-02 12:37:52</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•BeijingAPAC,BeijingBeijing</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Shenzhen</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,10 +4221,535 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-02 22:51:16</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>45</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426599394?refId=%2BZ7fCEvefwucXrznZiMB7g%3D%3D&amp;trackingId=fUm8A6bIlNSLBZfhhruFog%3D%3D</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>45</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=%2BZ7fCEvefwucXrznZiMB7g%3D%3D&amp;trackingId=qfTKUx4d9Ym3VZd8OQTOZQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Account Executive, Enterprise Platforms, Tier 2 Grower</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>40</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-platforms-tier-2-grower-at-stripe-4439345642?refId=%2BZ7fCEvefwucXrznZiMB7g%3D%3D&amp;trackingId=4Re%2BS7Aeo7kUC6rd8pE%2Bug%3D%3D</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Payment Partnerships Lead</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>75</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=ptP4cpGWzFa%2Bn7f5jTwgLw%3D%3D&amp;trackingId=QsxGJBjHr1dfnyHmr%2BH%2BNw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Manager, Customer Success</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>35</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/jobs/view/manager-customer-success-at-mastercard-4436642003?refId=fxXonN%2BxxgreSnQ8HKb8wA%3D%3D&amp;trackingId=f%2FNiLGg3r1iyuV9XV0%2F%2Fqw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Regional Customer Success Operations Manager</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>55</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/regional-customer-success-operations-manager-at-payoneer-4447800339?refId=guKIOclcPW1GsjY6%2BnYDpA%3D%3D&amp;trackingId=mK3Ff38FNWuEsmVpN4kUWA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•HangzhouAPAC,HangzhouHangzhou</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>30</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Account Executive, Mid-MarketSalesLondon</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>25</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f10a322a-1c17-47b3-822a-800ed524fbf6/account-executive-mid-market/</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Senior Manager, Financial Partnerships, Card Issuing &amp; Acquiring, EMEAFinancial and Strategic PartnershipsLondon</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>90</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0041178d-9b99-4c6e-9ad0-d8399d77559f/senior-manager-financial-partnerships-card-issuing-acquiring-emea/</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Business Solutions Director, Payments</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>50</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4447000136?refId=kVAro1n%2BYDOz0BQ9P3v2XQ%3D%3D&amp;trackingId=nqPJb7jFpuO3vLtTN5pDsA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>35</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447187427?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=raK2H4SHGFbyE%2FUoVkfrXQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>35</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447189411?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=RhpauV4iprOa2IHJ4bdLIQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>35</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447181514?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=P%2Bhrqpj%2FLbyfLyIQOwe4sA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>35</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447196241?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=45ea3%2Feu6IggyDw1q5Q5ng%3D%3D</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>JOB-20260802-0122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Customer Success &amp; Enterprise Support Lead, APAC</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>55</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/customer-success-enterprise-support-lead-apac-at-perplexity-4420517260?refId=VablemMtKM6216TcZiNvKg%3D%3D&amp;trackingId=U7KtZjcblD%2BJTzEqKl9ThQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -4870,7 +5395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4963,8 +5488,35 @@
       <c r="F3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:17</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>76</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>31</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -4981,7 +5533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9228,6 +9780,2955 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-ai-sales-grower/7954688</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426599394?refId=%2BZ7fCEvefwucXrznZiMB7g%3D%3D&amp;trackingId=fUm8A6bIlNSLBZfhhruFog%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=%2BZ7fCEvefwucXrznZiMB7g%3D%3D&amp;trackingId=qfTKUx4d9Ym3VZd8OQTOZQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-platforms-tier-2-grower-at-stripe-4439345642?refId=%2BZ7fCEvefwucXrznZiMB7g%3D%3D&amp;trackingId=4Re%2BS7Aeo7kUC6rd8pE%2Bug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=ptP4cpGWzFa%2Bn7f5jTwgLw%3D%3D&amp;trackingId=QsxGJBjHr1dfnyHmr%2BH%2BNw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/jobs/view/manager-customer-success-at-mastercard-4436642003?refId=fxXonN%2BxxgreSnQ8HKb8wA%3D%3D&amp;trackingId=f%2FNiLGg3r1iyuV9XV0%2F%2Fqw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/regional-customer-success-operations-manager-at-payoneer-4447800339?refId=guKIOclcPW1GsjY6%2BnYDpA%3D%3D&amp;trackingId=mK3Ff38FNWuEsmVpN4kUWA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f10a322a-1c17-47b3-822a-800ed524fbf6/account-executive-mid-market/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0041178d-9b99-4c6e-9ad0-d8399d77559f/senior-manager-financial-partnerships-card-issuing-acquiring-emea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/the-last-percentage-point-what-global-expansion-keeps-getting-wrong-about-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4453463006</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4447000136?refId=kVAro1n%2BYDOz0BQ9P3v2XQ%3D%3D&amp;trackingId=nqPJb7jFpuO3vLtTN5pDsA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447187427?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=raK2H4SHGFbyE%2FUoVkfrXQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447189411?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=RhpauV4iprOa2IHJ4bdLIQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447181514?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=P%2Bhrqpj%2FLbyfLyIQOwe4sA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447196241?refId=qHjnFreX7zZsrtyQjjhsmg%3D%3D&amp;trackingId=45ea3%2Feu6IggyDw1q5Q5ng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/customer-success-enterprise-support-lead-apac-at-perplexity-4420517260?refId=VablemMtKM6216TcZiNvKg%3D%3D&amp;trackingId=U7KtZjcblD%2BJTzEqKl9ThQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>dLocal</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dlocal/jobs/</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://uy.linkedin.com/company/dlocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nuvei/jobs/</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nuvei/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://fr.linkedin.com/company/okx</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:51:16</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-03 12:21:49</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4750,6 +4750,461 @@
         </is>
       </c>
       <c r="J123" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>45</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426599394?refId=4o8AkuklEXKYWypNDlBJYg%3D%3D&amp;trackingId=VZWKJIrjywNZ%2Fb%2B8Z30YYg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>45</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=4o8AkuklEXKYWypNDlBJYg%3D%3D&amp;trackingId=sApv3kBWyx6plsJ6I1zHlw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Payment Partnerships Lead</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>75</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=NtLjJFx3hp%2FmiXGvhPsE%2BQ%3D%3D&amp;trackingId=JlMhf2ejL%2BpeBk%2BJP866MA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Regional Customer Success Operations Manager</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>55</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/regional-customer-success-operations-manager-at-payoneer-4447800339?refId=LXSbM0uWfACyvYdeDNSsqg%3D%3D&amp;trackingId=FC1F8ahyaPrBf0h6aDJigw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>40</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446785559?refId=GrH6o6SnYoI6g1DyQKatXw%3D%3D&amp;trackingId=BdGZTr2FFQxtBUrsRu5Y7Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>40</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446755868?refId=GrH6o6SnYoI6g1DyQKatXw%3D%3D&amp;trackingId=V3hLddgH7iUtsP3MyNyM3w%3D%3D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>40</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-mexico-at-nuvei-4436810355?refId=GrH6o6SnYoI6g1DyQKatXw%3D%3D&amp;trackingId=lMjbqHaKEQVQDM57WFKJ5A%3D%3D</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>35</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447196241?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=N%2BFkbl%2Bw2pgXYVCXo987RQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>35</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447181514?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=gM56HgwVTxG8KV67tqzgug%3D%3D</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>35</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447187427?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=ENIEqq5SnKYg3ro7r21FFA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>35</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447189411?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=yQTLo5t6QQK6nhcvH0E1ow%3D%3D</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Lead, Payment Operations Strategy &amp; Automation</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>25</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/lead-payment-operations-strategy-and-automation-in-singapore-jid-3913</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>JOB-20260803-0135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Lead, Payment Operations Strategy &amp; Automation</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>25</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/lead-payment-operations-strategy-and-automation-in-singapore-jid-3913</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -5395,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5515,8 +5970,35 @@
       <c r="F4" t="n">
         <v>31</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -5533,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E309"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12729,6 +13211,2948 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-ai-sales-grower/7954688</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426599394?refId=4o8AkuklEXKYWypNDlBJYg%3D%3D&amp;trackingId=VZWKJIrjywNZ%2Fb%2B8Z30YYg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=4o8AkuklEXKYWypNDlBJYg%3D%3D&amp;trackingId=sApv3kBWyx6plsJ6I1zHlw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/payment-partnerships-lead-at-adyen-4390163388?refId=NtLjJFx3hp%2FmiXGvhPsE%2BQ%3D%3D&amp;trackingId=JlMhf2ejL%2BpeBk%2BJP866MA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/regional-customer-success-operations-manager-at-payoneer-4447800339?refId=LXSbM0uWfACyvYdeDNSsqg%3D%3D&amp;trackingId=FC1F8ahyaPrBf0h6aDJigw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b05c397a-d608-4684-aab9-ac65a10f8dce/account-executive-startups-ai-solutions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/the-last-percentage-point-what-global-expansion-keeps-getting-wrong-about-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446785559?refId=GrH6o6SnYoI6g1DyQKatXw%3D%3D&amp;trackingId=BdGZTr2FFQxtBUrsRu5Y7Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/jobs/view/business-development-manager-at-nuvei-4446755868?refId=GrH6o6SnYoI6g1DyQKatXw%3D%3D&amp;trackingId=V3hLddgH7iUtsP3MyNyM3w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-mexico-at-nuvei-4436810355?refId=GrH6o6SnYoI6g1DyQKatXw%3D%3D&amp;trackingId=lMjbqHaKEQVQDM57WFKJ5A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4453463006</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447196241?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=N%2BFkbl%2Bw2pgXYVCXo987RQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447181514?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=gM56HgwVTxG8KV67tqzgug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447187427?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=ENIEqq5SnKYg3ro7r21FFA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-customer-success-manager-at-ripple-4447189411?refId=%2Fn2TPChJ%2FadmZyWNlCgfiQ%3D%3D&amp;trackingId=yQTLo5t6QQK6nhcvH0E1ow%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/lead-payment-operations-strategy-and-automation-in-singapore-jid-3913</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/lead-payment-operations-strategy-and-automation-in-singapore-jid-3913</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fireblocks/jobs/</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/fireblocks/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Shenzhen</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Ningbo</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-03 12:21:49</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•HangzhouAPAC,HangzhouHangzhou</t>
+          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5205,6 +5205,461 @@
         </is>
       </c>
       <c r="J136" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>45</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426599394?refId=sjfy8P280azCeUTcp5gwBg%3D%3D&amp;trackingId=f%2B4gcXrtcDa7%2BfVA4xhW0Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Partner Solutions Architect, Technology Partnerships</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>45</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=sjfy8P280azCeUTcp5gwBg%3D%3D&amp;trackingId=OYZZuDp8N3klAyK7Wl%2FjvA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Account Executive, eCom KA, SME &amp; GrowthSalesSales•XiamenAPAC,XiamenXiamen</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>30</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1574051a-6b73-4f1a-bc6e-021c3e0e1bca/account-executive-ecom-ka-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Senior Manager, Financial Partnerships, Local Payment MethodsFinancial and Strategic PartnershipsAmericas, Sao Paulo</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>50</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/2cb5b8d6-73db-4f4d-bff4-ee66794dce8a/senior-manager-financial-partnerships-local-payment-methods/</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Senior Manager, GTM Solutions Architecture, AmericasOperations ManagementSan Francisco</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>60</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/59fb147e-d6ca-44ba-babe-008160e5c5af/senior-manager-gtm-solutions-architecture-americas/</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Manager, Sales Development Enterprise UK</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>25</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/manager-sales-development-enterprise-uk-at-airwallex-4446233957?refId=Ziwkc41hVtbxoHXyOALsZA%3D%3D&amp;trackingId=v3Nyic3Na1VJdCUrqbWPYw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Account Executive, eCom KA, SME &amp; Growth</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>25</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://cn.linkedin.com/jobs/view/account-executive-ecom-ka-sme-growth-at-airwallex-4349831634?refId=Ziwkc41hVtbxoHXyOALsZA%3D%3D&amp;trackingId=8MAlkhhLkiqm%2Fh24k4ndwQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Inside Nuvei's Customer Advisory Board: 7 things the smartest merchants think about payments in 2026|Nuveinuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026Nuvei CRO Laura Miller shares seven takeaways from two days with payments leaders at Beaverbrook: agentic commerce, fraud, and the fundamentals.</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>45</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Business Solutions Director, Payments</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>50</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Business DevelopmentBusiness Development Director - RippleXLondon, UK</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>40</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Best B2B Payment Solutions for 2026This is some text inside of a div block.This is some text inside of a div block.</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>40</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Solutions Engineering Lead</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>35</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/solutions-engineering-lead-in-london-jid-3924</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>JOB-20260804-0148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Solutions Engineering Lead</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>35</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/solutions-engineering-lead-in-london-jid-3924</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -5850,7 +6305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5997,8 +6452,35 @@
       <c r="F5" t="n">
         <v>34</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>76</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -6015,7 +6497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16153,6 +16635,2963 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-ai-sales-grower/7954688</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426599394?refId=sjfy8P280azCeUTcp5gwBg%3D%3D&amp;trackingId=f%2B4gcXrtcDa7%2BfVA4xhW0Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/partner-solutions-architect-technology-partnerships-at-stripe-4426717115?refId=sjfy8P280azCeUTcp5gwBg%3D%3D&amp;trackingId=OYZZuDp8N3klAyK7Wl%2FjvA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1574051a-6b73-4f1a-bc6e-021c3e0e1bca/account-executive-ecom-ka-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/2cb5b8d6-73db-4f4d-bff4-ee66794dce8a/senior-manager-financial-partnerships-local-payment-methods/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/59fb147e-d6ca-44ba-babe-008160e5c5af/senior-manager-gtm-solutions-architecture-americas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/manager-sales-development-enterprise-uk-at-airwallex-4446233957?refId=Ziwkc41hVtbxoHXyOALsZA%3D%3D&amp;trackingId=v3Nyic3Na1VJdCUrqbWPYw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>https://cn.linkedin.com/jobs/view/account-executive-ecom-ka-sme-growth-at-airwallex-4349831634?refId=Ziwkc41hVtbxoHXyOALsZA%3D%3D&amp;trackingId=8MAlkhhLkiqm%2Fh24k4ndwQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/solutions-engineering-lead-in-london-jid-3924</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/solutions-engineering-lead-in-london-jid-3924</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>dLocal</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dlocal/jobs/</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/dlocal/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nuvei/jobs/</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nuvei/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fireblocks/jobs/</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/fireblocks/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ripple/jobs/</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/ripple/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:52:56</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L149"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-02 10:45:38</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
+          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•Xi'anAPAC,Xi'anXi'an</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 08:56:40</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -5660,6 +5660,391 @@
         </is>
       </c>
       <c r="J149" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Account Executive, Enterprise - Grower</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>40</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Account Executive - Enterprise, Grower</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>40</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=BqtIJLV8pCcRJfoBmiE81g%3D%3D&amp;trackingId=ZSBSsCpoYaqe3fe3Y6qn3Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Director, Strategic Partnership Sales, Media Solutions</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>85</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446699664?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=Xzmv9ctNTbwzt%2F0vd1TSug%3D%3D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Project Manager, Commercial Integration &amp; Go-to-Market</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>25</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/project-manager-commercial-integration-go-to-market-at-mastercard-4446699663?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=EJTIuAH5snnP1auFOnMPgg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Director, Strategic Partnership Sales, Media Solutions</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>85</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446695884?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=pBCqdo7nLdUyxy2fBH7X9Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>40</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=CCKQdPjqvmHKzEmN0Fpo%2Fw%3D%3D&amp;trackingId=ZeJuT56EfZqscC0rxH8zZA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Senior Account Executive, Enterprise, CNSalesAPAC, Shanghai</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>45</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/ef549b3f-5c16-4597-bde0-3c47335c2868/senior-account-executive-enterprise-cn/</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, SME &amp; Growth (ANZ/SEA)SalesAPAC, Bangalore</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>45</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0793219c-3209-4b48-9df7-e100a13235ed/customer-success-manager-sme-growth-anz-sea/</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Account Executive, eCom KA, SME &amp; Growth</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>25</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://cn.linkedin.com/jobs/view/account-executive-ecom-ka-sme-growth-at-airwallex-4349732460?refId=0o6HgF%2B7d5lEaaNBxpyw6A%3D%3D&amp;trackingId=%2FECZA0vzd7UqVvQgZ4HYfw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>40</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=5QLvshJTNNiteMnmTJ58Xg%3D%3D&amp;trackingId=hdbPJScJz9OQ%2BvMsaosO9w%3D%3D</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Business Solutions Director, Payments</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>50</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=TSXKDn7TjTLonajIt9cdew%3D%3D&amp;trackingId=9mdfIKXr22X2cX307tTU1A%3D%3D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -6305,7 +6690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6479,8 +6864,35 @@
       <c r="F6" t="n">
         <v>37</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>76</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -6497,7 +6909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E561"/>
+  <dimension ref="A1:E682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19592,6 +20004,2813 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=BqtIJLV8pCcRJfoBmiE81g%3D%3D&amp;trackingId=ZSBSsCpoYaqe3fe3Y6qn3Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446699664?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=Xzmv9ctNTbwzt%2F0vd1TSug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/project-manager-commercial-integration-go-to-market-at-mastercard-4446699663?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=EJTIuAH5snnP1auFOnMPgg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446695884?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=pBCqdo7nLdUyxy2fBH7X9Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=CCKQdPjqvmHKzEmN0Fpo%2Fw%3D%3D&amp;trackingId=ZeJuT56EfZqscC0rxH8zZA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/9a87615c-17d7-4b94-b2ad-fb1e72c74e74/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/ef549b3f-5c16-4597-bde0-3c47335c2868/senior-account-executive-enterprise-cn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0793219c-3209-4b48-9df7-e100a13235ed/customer-success-manager-sme-growth-anz-sea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>https://cn.linkedin.com/jobs/view/account-executive-ecom-ka-sme-growth-at-airwallex-4349732460?refId=0o6HgF%2B7d5lEaaNBxpyw6A%3D%3D&amp;trackingId=%2FECZA0vzd7UqVvQgZ4HYfw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=5QLvshJTNNiteMnmTJ58Xg%3D%3D&amp;trackingId=hdbPJScJz9OQ%2BvMsaosO9w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=TSXKDn7TjTLonajIt9cdew%3D%3D&amp;trackingId=9mdfIKXr22X2cX307tTU1A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:56:40</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Ningbo</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•ChongqingAPAC,ChongqingChongqing</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•Xi'anAPAC,Xi'anXi'an</t>
+          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-02 12:37:52</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-04 13:52:56</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -5721,12 +5721,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=BqtIJLV8pCcRJfoBmiE81g%3D%3D&amp;trackingId=ZSBSsCpoYaqe3fe3Y6qn3Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=8nWMkbc7X8V8GRc%2BLrEO2g%3D%3D&amp;trackingId=oInjveIU8qee9yyHzfQLUg%3D%3D</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -5748,20 +5748,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Director, Strategic Partnership Sales, Media Solutions</t>
+          <t>Senior Specialist, Customer Success Operations &amp; Enablement</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446699664?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=Xzmv9ctNTbwzt%2F0vd1TSug%3D%3D</t>
+          <t>https://co.linkedin.com/jobs/view/senior-specialist-customer-success-operations-enablement-at-mastercard-4447342700?refId=KMrOAER7vxfM9upDMLh0kQ%3D%3D&amp;trackingId=pr0wQa%2BIsvHk6d1N9RW%2BrA%3D%3D</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -5783,20 +5783,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Project Manager, Commercial Integration &amp; Go-to-Market</t>
+          <t>Director, Strategic Partnership Sales, Media Solutions</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/jobs/view/project-manager-commercial-integration-go-to-market-at-mastercard-4446699663?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=EJTIuAH5snnP1auFOnMPgg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446690991?refId=KMrOAER7vxfM9upDMLh0kQ%3D%3D&amp;trackingId=PQtHyxKQ0tFICy%2FH0MsVEQ%3D%3D</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -5813,25 +5813,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Payoneer</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Director, Strategic Partnership Sales, Media Solutions</t>
+          <t>Senior Business Development Manager</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446695884?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=pBCqdo7nLdUyxy2fBH7X9Q%3D%3D</t>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=IzKUk34L6YpgjT6GZkiUdg%3D%3D&amp;trackingId=KsswUqORpfX1pxJwhVAIyQ%3D%3D</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Payoneer</t>
+          <t>Nuvei</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Senior Business Development Manager</t>
+          <t>Business Development Manager</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=CCKQdPjqvmHKzEmN0Fpo%2Fw%3D%3D&amp;trackingId=ZeJuT56EfZqscC0rxH8zZA%3D%3D</t>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=fQQm06Qjtt1Kgt7MMb9idA%3D%3D&amp;trackingId=0aLHfqQqPLs5hyouFhhtCQ%3D%3D</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -5883,25 +5883,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Fireblocks</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Senior Account Executive, Enterprise, CNSalesAPAC, Shanghai</t>
+          <t>Business Solutions Director, Payments</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/job/ef549b3f-5c16-4597-bde0-3c47335c2868/senior-account-executive-enterprise-cn/</t>
+          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=n%2B2EpXDj6ta9mcQ%2BLLCyoQ%3D%3D&amp;trackingId=3DhZc%2FnjPDhp3yu3IGNUVA%3D%3D</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -5918,25 +5918,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>BVNK</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Customer Success Manager, SME &amp; Growth (ANZ/SEA)SalesAPAC, Bangalore</t>
+          <t>Business Development Specialist jobs</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/job/0793219c-3209-4b48-9df7-e100a13235ed/customer-success-manager-sme-growth-anz-sea/</t>
+          <t>https://www.linkedin.com/jobs/business-development-specialist-jobs?trk=organization_guest_linkster_link</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>StraitsX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Account Executive, eCom KA, SME &amp; Growth</t>
+          <t>Product Manager, Payments</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cn.linkedin.com/jobs/view/account-executive-ecom-ka-sme-growth-at-airwallex-4349732460?refId=0o6HgF%2B7d5lEaaNBxpyw6A%3D%3D&amp;trackingId=%2FECZA0vzd7UqVvQgZ4HYfw%3D%3D</t>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=Jg%2Bkpr0quNbs70FsZltDKA%3D%3D&amp;trackingId=%2FdUvQ3BUn9zjMkpOEoh0fg%3D%3D</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -5988,25 +5988,25 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Nuvei</t>
+          <t>StraitsX</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Business Development Manager</t>
+          <t>Commercial Sales Associate</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=5QLvshJTNNiteMnmTJ58Xg%3D%3D&amp;trackingId=hdbPJScJz9OQ%2BvMsaosO9w%3D%3D</t>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4445135478?refId=Jg%2Bkpr0quNbs70FsZltDKA%3D%3D&amp;trackingId=31WcEw8Hedxw59yt%2BmPdoA%3D%3D</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -6023,34 +6023,494 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>40</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/business-development-representative-at-perplexity-4362512479?refId=6qaPwc%2FbMr%2BTEuNbcyxwFA%3D%3D&amp;trackingId=0IPFNFE%2BxsvTQJoXuYnTbw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:46:08</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Account Executive - Enterprise, Grower</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>40</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=B44ZYpaXSSJX8NIh6WTvVQ%3D%3D&amp;trackingId=qHFM72g2d9vzdcldSClVpQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Customer Success Operations &amp; Enablement</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>55</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-specialist-customer-success-operations-enablement-at-mastercard-4447342700?refId=jh2%2FtOAiDmvdFmXVMQLwUQ%3D%3D&amp;trackingId=Rf77WcqIVtmHHKOL0R5Rkg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Director, Strategic Partnership Sales, Media Solutions</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>85</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4447302630?refId=jh2%2FtOAiDmvdFmXVMQLwUQ%3D%3D&amp;trackingId=cHuOlN6FX77m3P5TFWliBA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>40</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=fN%2FwaysIciAPniLOMUfXig%3D%3D&amp;trackingId=D6GjWYxbm40hQyaX0d4C5A%3D%3D</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Director, Strategic Partnerships APACFinancial and Strategic PartnershipsFinancial and Strategic Partnerships•SingaporeAPAC,SingaporeSingapore</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>45</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/5f86d8ab-9b0c-4bd9-ab6e-efa0cda538ab/director-strategic-partnerships-apac/</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Director, Sales, EnterpriseSalesSales•San FranciscoAmericas,San FranciscoSan Francisco</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>25</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/92e5b670-da4a-4cc3-94ed-740ff37d68df/director-sales-enterprise/</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Account Executive, Embedded Finance &amp; PlatformsSalesAPAC, Melbourne</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>25</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/3227ad3d-69f4-4417-8fcc-cb5f51c67d1b/account-executive-embedded-finance-platforms/</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Solutions Architect – PaymentsEngineeringSydney</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>45</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d93e16f2-fea9-458b-a842-6e10b2fa2bdd/solutions-architect-payments/</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>40</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=ZXgQlfLjiPTyZx9TTJ9%2BBQ%3D%3D&amp;trackingId=aAtMuA%2FVaETGQ2u6wAT%2FUA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>Fireblocks</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>Business Solutions Director, Payments</t>
         </is>
       </c>
-      <c r="F160" t="n">
+      <c r="F170" t="n">
         <v>50</v>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=TSXKDn7TjTLonajIt9cdew%3D%3D&amp;trackingId=9mdfIKXr22X2cX307tTU1A%3D%3D</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>2026-08-05 08:56:40</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=FaYVCBhEoAwDO%2BIbAicFxQ%3D%3D&amp;trackingId=wT%2BRo3bhbfUdbcID4SZSHQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Product Manager, Payments</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>25</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=VpYcKxQOwjesmQb4F2t1Bg%3D%3D&amp;trackingId=WUiN6v%2BMCVK3qzc6UaJt2w%3D%3D</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Commercial Sales Associate</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>25</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4445135478?refId=VpYcKxQOwjesmQb4F2t1Bg%3D%3D&amp;trackingId=Mc6yYGkwux5mFzjibJvAfg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>40</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/business-development-representative-at-perplexity-4362512479?refId=vDaAltLruj8Ard0%2BS%2BaMPA%3D%3D&amp;trackingId=TbtIMJsHh0BB7b4TLpvhbg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"New,Watching,Applied,Interview,Rejected,Offer"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6690,7 +7150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6873,7 +7333,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6889,10 +7349,36 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>76</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -6909,7 +7395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E682"/>
+  <dimension ref="A1:E779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20007,7 +20493,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -20029,7 +20515,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -20051,7 +20537,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -20073,7 +20559,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -20095,7 +20581,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -20117,7 +20603,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -20139,7 +20625,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -20154,14 +20640,14 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=BqtIJLV8pCcRJfoBmiE81g%3D%3D&amp;trackingId=ZSBSsCpoYaqe3fe3Y6qn3Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=8nWMkbc7X8V8GRc%2BLrEO2g%3D%3D&amp;trackingId=oInjveIU8qee9yyHzfQLUg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -20183,7 +20669,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -20198,14 +20684,14 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446699664?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=Xzmv9ctNTbwzt%2F0vd1TSug%3D%3D</t>
+          <t>https://co.linkedin.com/jobs/view/senior-specialist-customer-success-operations-enablement-at-mastercard-4447342700?refId=KMrOAER7vxfM9upDMLh0kQ%3D%3D&amp;trackingId=pr0wQa%2BIsvHk6d1N9RW%2BrA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -20220,14 +20706,14 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/jobs/view/project-manager-commercial-integration-go-to-market-at-mastercard-4446699663?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=EJTIuAH5snnP1auFOnMPgg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446690991?refId=KMrOAER7vxfM9upDMLh0kQ%3D%3D&amp;trackingId=PQtHyxKQ0tFICy%2FH0MsVEQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -20237,41 +20723,41 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Payoneer</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4446695884?refId=VMygY0HgGzq5qQywdkHglg%3D%3D&amp;trackingId=pBCqdo7nLdUyxy2fBH7X9Q%3D%3D</t>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=IzKUk34L6YpgjT6GZkiUdg%3D%3D&amp;trackingId=KsswUqORpfX1pxJwhVAIyQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Payoneer</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=CCKQdPjqvmHKzEmN0Fpo%2Fw%3D%3D&amp;trackingId=ZeJuT56EfZqscC0rxH8zZA%3D%3D</t>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -20286,14 +20772,14 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/job/9a87615c-17d7-4b94-b2ad-fb1e72c74e74/account-executive-outbound-sme-growth/</t>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -20308,58 +20794,58 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Nium</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/job/ef549b3f-5c16-4597-bde0-3c47335c2868/senior-account-executive-enterprise-cn/</t>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Nium</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/job/0793219c-3209-4b48-9df7-e100a13235ed/customer-success-manager-sme-growth-anz-sea/</t>
+          <t>https://www.nium.com/solutions/marketplaces</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -20369,19 +20855,19 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Nium</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+          <t>https://www.nium.com/solutions/airlines</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -20391,41 +20877,41 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Nium</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Nium</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>https://cn.linkedin.com/jobs/view/account-executive-ecom-ka-sme-growth-at-airwallex-4349732460?refId=0o6HgF%2B7d5lEaaNBxpyw6A%3D%3D&amp;trackingId=%2FECZA0vzd7UqVvQgZ4HYfw%3D%3D</t>
+          <t>https://www.nium.com/solutions/marketplaces</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -20440,14 +20926,14 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+          <t>https://www.nium.com/solutions/airlines</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -20457,19 +20943,19 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Nium</t>
+          <t>Checkout.com</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
+          <t>https://www.checkout.com/products/payment-links</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -20479,19 +20965,19 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Nium</t>
+          <t>Nuvei</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>https://www.nium.com/solutions/airlines</t>
+          <t>https://www.nuvei.com/payment-solution</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -20501,19 +20987,19 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Nium</t>
+          <t>Nuvei</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -20523,19 +21009,19 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Nium</t>
+          <t>Nuvei</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -20545,19 +21031,19 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Nium</t>
+          <t>Nuvei</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>https://www.nium.com/solutions/airlines</t>
+          <t>https://www.nuvei.com/use-cases/government</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -20567,19 +21053,19 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Checkout.com</t>
+          <t>Nuvei</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>https://www.checkout.com/products/payment-links</t>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -20594,14 +21080,14 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/payment-solution</t>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -20616,14 +21102,14 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/online-retail</t>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -20638,14 +21124,14 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -20660,14 +21146,14 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -20682,14 +21168,14 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+          <t>https://www.nuvei.com/solutions/issuing</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -20704,14 +21190,14 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+          <t>https://www.nuvei.com/solutions/apm</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -20726,14 +21212,14 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -20748,14 +21234,14 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -20770,14 +21256,14 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -20792,14 +21278,14 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/issuing</t>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -20814,14 +21300,14 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/apm</t>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -20836,14 +21322,14 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -20858,14 +21344,14 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -20880,14 +21366,14 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -20902,14 +21388,14 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -20924,14 +21410,14 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -20946,14 +21432,14 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/currency-management</t>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -20968,14 +21454,14 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -20990,14 +21476,14 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -21012,14 +21498,14 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -21034,14 +21520,14 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/hospitality</t>
+          <t>https://www.nuvei.com/use-cases/government</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -21056,14 +21542,14 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/automotive</t>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -21078,14 +21564,14 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/grocery</t>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -21100,14 +21586,14 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -21122,14 +21608,14 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -21144,14 +21630,14 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -21166,14 +21652,14 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -21188,14 +21674,14 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -21210,19 +21696,19 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -21232,14 +21718,14 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=fQQm06Qjtt1Kgt7MMb9idA%3D%3D&amp;trackingId=0aLHfqQqPLs5hyouFhhtCQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -21249,19 +21735,19 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Nuvei</t>
+          <t>Fireblocks</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -21271,19 +21757,19 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Nuvei</t>
+          <t>Fireblocks</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -21293,19 +21779,19 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Nuvei</t>
+          <t>Fireblocks</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -21315,46 +21801,46 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Nuvei</t>
+          <t>Fireblocks</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Nuvei</t>
+          <t>Fireblocks</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=5QLvshJTNNiteMnmTJ58Xg%3D%3D&amp;trackingId=hdbPJScJz9OQ%2BvMsaosO9w%3D%3D</t>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -21364,14 +21850,14 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=n%2B2EpXDj6ta9mcQ%2BLLCyoQ%3D%3D&amp;trackingId=3DhZc%2FnjPDhp3yu3IGNUVA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -21386,14 +21872,14 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -21403,19 +21889,19 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Fireblocks</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -21425,19 +21911,19 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Fireblocks</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -21447,63 +21933,63 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Fireblocks</t>
+          <t>Paxos</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Fireblocks</t>
+          <t>BVNK</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=TSXKDn7TjTLonajIt9cdew%3D%3D&amp;trackingId=9mdfIKXr22X2cX307tTU1A%3D%3D</t>
+          <t>https://www.bvnk.com/self-managed-payments</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Fireblocks</t>
+          <t>BVNK</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+          <t>https://www.linkedin.com/jobs/business-development-specialist-jobs?trk=organization_guest_linkster_link</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -21513,19 +21999,19 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>BitPay</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+          <t>https://bitpay.com/careers/directory</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -21535,19 +22021,19 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>BitPay</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+          <t>https://bitpay.com/careers/directory</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -21557,19 +22043,19 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Paxos</t>
+          <t>BitPay</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+          <t>https://bitpay.com/careers/directory</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -21579,19 +22065,19 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>BVNK</t>
+          <t>BitPay</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>https://www.bvnk.com/self-managed-payments</t>
+          <t>https://bitpay.com/careers/directory</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -21613,7 +22099,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -21623,19 +22109,19 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>BitPay</t>
+          <t>Triple-A</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>https://bitpay.com/careers/directory</t>
+          <t>https://triple-a.io/case-studies</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -21645,63 +22131,63 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>BitPay</t>
+          <t>Triple-A</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>https://bitpay.com/careers/directory</t>
+          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>BitPay</t>
+          <t>StraitsX</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>https://bitpay.com/careers/directory</t>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=Jg%2Bkpr0quNbs70FsZltDKA%3D%3D&amp;trackingId=%2FdUvQ3BUn9zjMkpOEoh0fg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>BitPay</t>
+          <t>StraitsX</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>https://bitpay.com/careers/directory</t>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4445135478?refId=Jg%2Bkpr0quNbs70FsZltDKA%3D%3D&amp;trackingId=31WcEw8Hedxw59yt%2BmPdoA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -21711,19 +22197,19 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Triple-A</t>
+          <t>Unlimit</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>https://triple-a.io/case-studies</t>
+          <t>https://unlimit.com/ma</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -21733,19 +22219,19 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Triple-A</t>
+          <t>Unlimit</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
+          <t>https://unlimit.com/ma</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -21760,14 +22246,14 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>https://unlimit.com/ma</t>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -21782,14 +22268,14 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>https://unlimit.com/ma</t>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -21804,14 +22290,14 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -21826,36 +22312,36 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Unlimit</t>
+          <t>Perplexity</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+          <t>https://www.linkedin.com/jobs/view/business-development-representative-at-perplexity-4362512479?refId=6qaPwc%2FbMr%2BTEuNbcyxwFA%3D%3D&amp;trackingId=0IPFNFE%2BxsvTQJoXuYnTbw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -21865,19 +22351,19 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Unlimit</t>
+          <t>Wise</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -21892,14 +22378,14 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -21914,14 +22400,14 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -21943,7 +22429,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -21958,80 +22444,95 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
+          <t>https://wise.jobs/wise-platform</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>SCAN_FAILED</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Wise</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>SCAN_FAILED</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Wise</t>
+          <t>Checkout.com</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>SCAN_FAILED</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Wise</t>
+          <t>Thunes</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>https://wise.jobs/wise-platform</t>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -22041,24 +22542,24 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Rapyd</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>https://jobs.visa.com/</t>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -22068,24 +22569,24 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Checkout.com</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -22095,24 +22596,24 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Thunes</t>
+          <t>BitPay</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -22122,24 +22623,24 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Rapyd</t>
+          <t>StraitsX</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+          <t>https://www.straitsx.com/careers</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -22149,24 +22650,24 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>OSL</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circle/jobs/</t>
+          <t>https://osl.com/careers/</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -22176,24 +22677,24 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>BitPay</t>
+          <t>Unlimit</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -22203,24 +22704,24 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Triple-A</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+          <t>https://www.okx.com/careers</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -22230,24 +22731,24 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>StraitsX</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>https://www.straitsx.com/careers</t>
+          <t>https://www.gate.io/careers</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -22257,24 +22758,24 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>StraitsX</t>
+          <t>Reap</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -22284,24 +22785,24 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>OSL</t>
+          <t>Mesh</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>https://osl.com/careers/</t>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -22311,24 +22812,24 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>OSL</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group</t>
+          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -22338,24 +22839,24 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Tazapay</t>
+          <t>Skyfire</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+          <t>https://www.skyfire.xyz/careers</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -22365,24 +22866,24 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Unlimit</t>
+          <t>Skyfire</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -22392,24 +22893,24 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Nevermined</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>https://www.okx.com/careers</t>
+          <t>https://nevermined.io/careers</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -22419,24 +22920,24 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Nevermined</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/okx/jobs/</t>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -22446,24 +22947,24 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>https://www.gate.io/careers</t>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -22473,24 +22974,24 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 16:46:08</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -22500,314 +23001,2473 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Reap</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Mesh</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-      <c r="E672" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
-        </is>
-      </c>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Skyfire</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>https://www.skyfire.xyz/careers</t>
-        </is>
-      </c>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Skyfire</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Nevermined</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>https://nevermined.io/careers</t>
-        </is>
-      </c>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Nevermined</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openai/jobs/</t>
-        </is>
-      </c>
-      <c r="E678" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=B44ZYpaXSSJX8NIh6WTvVQ%3D%3D&amp;trackingId=qHFM72g2d9vzdcldSClVpQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
-        </is>
-      </c>
-      <c r="E679" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Perplexity</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
-        </is>
-      </c>
-      <c r="E680" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+          <t>https://co.linkedin.com/jobs/view/senior-specialist-customer-success-operations-enablement-at-mastercard-4447342700?refId=jh2%2FtOAiDmvdFmXVMQLwUQ%3D%3D&amp;trackingId=Rf77WcqIVtmHHKOL0R5Rkg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>SCAN_FAILED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+          <t>https://www.linkedin.com/jobs/view/director-strategic-partnership-sales-media-solutions-at-mastercard-4447302630?refId=jh2%2FtOAiDmvdFmXVMQLwUQ%3D%3D&amp;trackingId=cHuOlN6FX77m3P5TFWliBA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-08-05 08:56:40</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=fN%2FwaysIciAPniLOMUfXig%3D%3D&amp;trackingId=D6GjWYxbm40hQyaX0d4C5A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/5f86d8ab-9b0c-4bd9-ab6e-efa0cda538ab/director-strategic-partnerships-apac/</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/92e5b670-da4a-4cc3-94ed-740ff37d68df/director-sales-enterprise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/3227ad3d-69f4-4417-8fcc-cb5f51c67d1b/account-executive-embedded-finance-platforms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d93e16f2-fea9-458b-a842-6e10b2fa2bdd/solutions-architect-payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=ZXgQlfLjiPTyZx9TTJ9%2BBQ%3D%3D&amp;trackingId=aAtMuA%2FVaETGQ2u6wAT%2FUA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/business-solutions-director-payments-at-fireblocks-4448365719?refId=FaYVCBhEoAwDO%2BIbAicFxQ%3D%3D&amp;trackingId=wT%2BRo3bhbfUdbcID4SZSHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=VpYcKxQOwjesmQb4F2t1Bg%3D%3D&amp;trackingId=WUiN6v%2BMCVK3qzc6UaJt2w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4445135478?refId=VpYcKxQOwjesmQb4F2t1Bg%3D%3D&amp;trackingId=Mc6yYGkwux5mFzjibJvAfg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/business-development-representative-at-perplexity-4362512479?refId=vDaAltLruj8Ard0%2BS%2BaMPA%3D%3D&amp;trackingId=TbtIMJsHh0BB7b4TLpvhbg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
           <t>SCAN_FAILED</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D682" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/wise/jobs/</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:06:50</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
         </is>
       </c>
     </row>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L173"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
+          <t>Account Executive, Outbound, SME &amp; GrowthSalesAPAC, Shanghai</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-02 12:37:52</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -6500,6 +6500,286 @@
         </is>
       </c>
       <c r="J173" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Account Executive - Enterprise, Grower</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>40</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=Lkhyo7WSiy5nY%2Fco0H%2B5Kw%3D%3D&amp;trackingId=xINHMX6Wc1miLlmNWv%2B8rQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Customer Success Operations &amp; Enablement</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>55</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-specialist-customer-success-operations-enablement-at-mastercard-4447342700?refId=vPDVQ2Rf2X92%2BVVLf2b4AA%3D%3D&amp;trackingId=rCVjxbg7Y2q0GQI5B8qRUQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>40</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=t3e81OeZtssvrFw81N0ppw%3D%3D&amp;trackingId=6rX%2BguMQdP1XTn76h4DBRw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, SME &amp; GrowthSalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>45</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/bda9aaa5-f2ab-4968-a7b0-ea097ab925a6/customer-success-manager-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>(Senior) Account Executive, EnterpriseSalesSales•ShanghaiAPAC,ShanghaiShanghai</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>45</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/68bbcf0d-21de-420c-af28-0425663cae94/senior-account-executive-enterprise/</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Manager, Growth Strategy &amp; OperationsOperations ManagementOperations Management•SingaporeAPAC,SingaporeSingapore</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>25</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f22a8795-d79c-4b80-8e92-92f724d3d23f/manager-growth-strategy-operations/</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Senior Account Executive, EnterpriseSalesAPAC, Melbourne</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>45</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d6a11fda-76e0-439f-ab2f-bbdfd80d9da8/senior-account-executive-enterprise/</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>JOB-20260805-0180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>40</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=Hxk0ZTXfyPpcvRib1ejc9A%3D%3D&amp;trackingId=yHsodyuaouuUGEA%2FCRcFDw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -7150,7 +7430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7379,6 +7659,34 @@
         <v>16</v>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -7395,7 +7703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E779"/>
+  <dimension ref="A1:E904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25471,6 +25779,2946 @@
         </is>
       </c>
     </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-executive-enterprise-grower-at-stripe-4426523295?refId=Lkhyo7WSiy5nY%2Fco0H%2B5Kw%3D%3D&amp;trackingId=xINHMX6Wc1miLlmNWv%2B8rQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-specialist-customer-success-operations-enablement-at-mastercard-4447342700?refId=vPDVQ2Rf2X92%2BVVLf2b4AA%3D%3D&amp;trackingId=rCVjxbg7Y2q0GQI5B8qRUQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=t3e81OeZtssvrFw81N0ppw%3D%3D&amp;trackingId=6rX%2BguMQdP1XTn76h4DBRw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/bda9aaa5-f2ab-4968-a7b0-ea097ab925a6/customer-success-manager-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/68bbcf0d-21de-420c-af28-0425663cae94/senior-account-executive-enterprise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f22a8795-d79c-4b80-8e92-92f724d3d23f/manager-growth-strategy-operations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/9a87615c-17d7-4b94-b2ad-fb1e72c74e74/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d6a11fda-76e0-439f-ab2f-bbdfd80d9da8/senior-account-executive-enterprise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/business-development-manager-at-nuvei-4448277899?refId=Hxk0ZTXfyPpcvRib1ejc9A%3D%3D&amp;trackingId=yHsodyuaouuUGEA%2FCRcFDw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/blog/best-b2b-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>https://careers.mastercard.com/</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://careers.mastercard.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>https://www.thunes.com/careers/</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.thunes.com/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>https://www.circle.com/careers</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://careers.circle.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/coinbase/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fireblocks/jobs/</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/fireblocks/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ripple/jobs/</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/ripple/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/paxos/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:35:46</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•ChongqingAPAC,ChongqingChongqing</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Chongqing</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
+          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•YiwuAPAC,YiwuYiwu</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-04 13:52:56</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -6780,6 +6780,426 @@
         </is>
       </c>
       <c r="J181" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Risk Operations Program Manager</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>40</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=CRGBPZo5QspVXs51vTqPbA%3D%3D&amp;trackingId=gKHDOPwsF0vw592xSqrn%2FA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Business Analyst - Operations</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>25</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=wqPotDhAyzVWnFipJahFLA%3D%3D&amp;trackingId=BLDzhw32HTPGWMIqKkU6hQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>40</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=fTbgYUA7yK3sL%2Be%2BTa61ig%3D%3D&amp;trackingId=TJJCjJpsT0JWex4YFVQCUA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Director, Channel Partnerships, SME &amp; Growth, AmericasSalesSales•Mexico CityAmericas,Mexico CityMexico City</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>55</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/741af157-0000-4097-b13c-1e4677a7db49/director-channel-partnerships-sme-growth-americas/</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Senior Manager, Strategic Partnerships, EMEAFinancial and Strategic PartnershipsFinancial and Strategic Partnerships•AmsterdamAmsterdam,EMEAAmsterdam</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>45</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/76737659-4f27-450f-8f7b-f690723faad5/senior-manager-strategic-partnerships-emea/</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>GTM Partnerships Manager, SME &amp; GrowthSalesAPAC, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>25</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/288d26cf-6dd4-4da9-912c-d082d388928f/gtm-partnerships-manager-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Senior Manager, Financial Partnerships, Banking &amp; New Market Development, EMEAFinancial and Strategic PartnershipsLondon</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>45</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f5acfb5f-c352-4099-8443-101551777f35/senior-manager-financial-partnerships-banking-new-market-development-emea/</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Enterprise</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>55</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/customer-success-manager-enterprise-at-airwallex-4448014733?refId=CCvuHs%2Bb58QtjwkmbT8nBQ%3D%3D&amp;trackingId=XYvmugyc3JbbJ5NeBrPPdQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Nuvei and BlackLine Partner to Modernize the Invoice-to-Cash Process Through Embedded Payments|Nuveinuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-paymentsEnterprises can now accept payments directly inside BlackLine, shortening collection cycles, removing manual reconciliation steps, and improving cash flow visibilityEnterprises can now accept payments directly inside BlackLine, shortening collection cycles, removing manual reconciliation steps, and improving cash flow visibility</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>35</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Why travel is the hardest test for agentic commerce|Nuveinuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerceTravel booking exposes the biggest challenges in agentic commerce: high-value purchases, limited reversibility, and the need for trust between AI platforms, merchants, banks, and payment providers.</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>40</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>40</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=PykoDehuXWHMslcrUEHQyQ%3D%3D&amp;trackingId=4u2So7gssA%2FdeJgwSAjXAA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>VP, Customer Success</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>35</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=yoz2WRjwXCCh9YF2yoBcbA%3D%3D&amp;trackingId=qzvN5c%2FT7o470WzcOl3dcw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -7430,7 +7850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7685,8 +8105,35 @@
       <c r="F9" t="n">
         <v>38</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>76</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -7703,7 +8150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E904"/>
+  <dimension ref="A1:E1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28719,6 +29166,2830 @@
         </is>
       </c>
     </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=CRGBPZo5QspVXs51vTqPbA%3D%3D&amp;trackingId=gKHDOPwsF0vw592xSqrn%2FA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=wqPotDhAyzVWnFipJahFLA%3D%3D&amp;trackingId=BLDzhw32HTPGWMIqKkU6hQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=fTbgYUA7yK3sL%2Be%2BTa61ig%3D%3D&amp;trackingId=TJJCjJpsT0JWex4YFVQCUA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/741af157-0000-4097-b13c-1e4677a7db49/director-channel-partnerships-sme-growth-americas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/76737659-4f27-450f-8f7b-f690723faad5/senior-manager-strategic-partnerships-emea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/288d26cf-6dd4-4da9-912c-d082d388928f/gtm-partnerships-manager-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f5acfb5f-c352-4099-8443-101551777f35/senior-manager-financial-partnerships-banking-new-market-development-emea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/customer-success-manager-enterprise-at-airwallex-4448014733?refId=CCvuHs%2Bb58QtjwkmbT8nBQ%3D%3D&amp;trackingId=XYvmugyc3JbbJ5NeBrPPdQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=PykoDehuXWHMslcrUEHQyQ%3D%3D&amp;trackingId=4u2So7gssA%2FdeJgwSAjXAA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=yoz2WRjwXCCh9YF2yoBcbA%3D%3D&amp;trackingId=qzvN5c%2FT7o470WzcOl3dcw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-08-06 08:52:31</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,23 +12,33 @@
     <sheet name="Run_Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,8 +430,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L193"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L228"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -511,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +556,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +626,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +661,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +696,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +836,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +976,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1011,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1046,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1081,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1116,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1151,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1186,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1361,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1396,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:05:08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1571,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1641,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1711,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1781,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1816,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2108,7 +2118,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Chongqing</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Fuzhou</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2131,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2226,7 +2236,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2271,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2446,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2481,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2516,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2551,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2586,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2621,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2761,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2796,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2831,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2866,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2901,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2936,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2971,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +3006,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3041,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3076,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3111,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3146,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3181,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3216,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3251,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3286,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3321,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3356,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3391,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3426,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3461,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3496,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3531,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3566,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3601,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3636,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3671,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3706,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4186,7 +4196,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4231,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5481,7 +5491,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -5516,7 +5526,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5551,7 +5561,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:05:08</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5691,7 +5701,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -6238,7 +6248,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Director, Sales, EnterpriseSalesSales•San FranciscoAmericas,San FranciscoSan Francisco</t>
+          <t>Director, Sales, EnterpriseSalesSales•New YorkAmericas,New YorkNew York</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -6251,7 +6261,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-08-05 17:06:50</t>
+          <t>2026-08-06 17:00:32</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -6693,7 +6703,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Manager, Growth Strategy &amp; OperationsOperations ManagementOperations Management•SingaporeAPAC,SingaporeSingapore</t>
+          <t>Manager, Growth Strategy &amp; OperationsOperations ManagementAPAC, Singapore</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -6706,7 +6716,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -6728,7 +6738,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Senior Account Executive, EnterpriseSalesAPAC, Melbourne</t>
+          <t>Senior Account Executive, EnterpriseSalesSales•MelbourneAPAC,MelbourneMelbourne</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -6741,7 +6751,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-06 17:05:08</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -6916,7 +6926,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -6951,7 +6961,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:00:32</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -7091,7 +7101,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7126,7 +7136,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-06 17:23:41</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -7200,6 +7210,1239 @@
         </is>
       </c>
       <c r="J193" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Program Manager, Commercial Solutions</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>75</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=N8obzet0IS2NiT5dNqscYw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Risk Operations Program Manager</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>40</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=J8r8nLy7YGe%2Bfoh2JQ7%2BMA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Business Analyst - Operations</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>25</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=S5PbcpiOC9GR7SVXE2zaZg%3D%3D&amp;trackingId=Ms96hphPrllh3LW3Gg4tAQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>40</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=wOyv7m64G4LcWofHoL26Ag%3D%3D&amp;trackingId=Q0addY%2B7DR6IbHAoGvKNPw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Account Executive/Senior Account Executive, Enterprise (Travel Vertical)SalesAPAC, Jakarta</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>45</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b2a5c56c-2691-4c4e-b522-5f635ac7d4d5/account-executive-senior-account-executive-enterprise-travel-vertical/</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Enterprise</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>55</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/customer-success-manager-enterprise-at-airwallex-4448014733?refId=BJq1GyANRgi2MTpWYhweXQ%3D%3D&amp;trackingId=LPn453ZuNmxMk%2FEUTZAVFQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>40</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=162bByYUJ39qrVdO%2FnKa9Q%3D%3D&amp;trackingId=gjBNN7gBif7eGxC6YGS%2Fng%3D%3D</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>VP, Customer Success</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>35</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=vYrn4cTHAhuLiz3lOMTo6Q%3D%3D&amp;trackingId=TIbqVPZ5rPGFtLdzqsAo3A%3D%3D</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Commercial Sales Associate</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>25</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=4gqmXWpBaou6yWX0%2FnoDrQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Product Manager, Payments</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>25</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=e9kZxmJeV9RCs9NvpdwWVA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Program Manager, Commercial Solutions</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>75</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=TKgG8RBffmQ1EIKmz7f5xA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Risk Operations Program Manager</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>40</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=H%2B7gh74YvgVeWneRPlvSgA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Business Analyst - Operations</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>25</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=raK%2BYE%2B6Zn4NV5U20tR7yQ%3D%3D&amp;trackingId=orMwWTNn5yXw6HVjn%2BnVFQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>40</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=%2BVePhyqV1UK7m%2BEpemW%2Bqw%3D%3D&amp;trackingId=MfFMDjXZ7AEFjcm%2BLDClfQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>40</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=Eu3zauL8%2BVQYxswknWjyqw%3D%3D&amp;trackingId=jqTc9z9Y%2FhFLbXJptbUyCg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Account Executive, Enterprise Spend – Benelux &amp; NordicsSalesAmsterdam, EMEA</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>45</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/8e7e3a2c-c593-49a7-959b-323b7aa57662/account-executive-enterprise-spend-benelux-nordics/</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Senior Manager, Growth InnovationOperations ManagementAmericas, San Francisco</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>25</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/810d3f46-9b64-4d96-85a0-2302658153ba/senior-manager-growth-innovation/</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Senior Manager, Financial Partnerships APACFinancial and Strategic PartnershipsAPAC, Sydney</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>45</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/00a7bbce-af16-4d4d-b36b-50034b5d9038/senior-manager-financial-partnerships-apac/</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>40</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=FhkshE6excHUzWGc6mBoaw%3D%3D&amp;trackingId=LIbaGvcZ2dKomCb9H8QJdg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>VP, Customer Success</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>35</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=ZmDFvJaPiEETvvTPYoCdJA%3D%3D&amp;trackingId=p8GbjFst2c1nAm%2FRSX1TIQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Commercial Sales Associate</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>25</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=BrUnoPz20RnN3FATtQcPvw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Product Manager, Payments</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>25</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=VWk%2Bgp3VbNROKLEt%2B94Bhw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>APAC Export Lead, Ads Solutions</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>35</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/apac-export-lead-ads-solutions-at-openai-4449314412?refId=gRYPAAzUH306VeNbRdZfPA%3D%3D&amp;trackingId=Ja4zQEB%2BpuSFiODzbUgtvw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Program Manager, Commercial Solutions</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>75</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=TWU%2FE1Gu57Xywn4UfRn0ng%3D%3D</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Risk Operations Program Manager</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>40</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=%2BhAShAezY95tBh3RyiIvfQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Business Analyst - Operations</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=42LfBSOufBhvYUAOL7Y9gw%3D%3D&amp;trackingId=4HSiuDEF191PdMumcLWYLw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>40</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=aK3Yk7SO5lStab1R44KsRw%3D%3D&amp;trackingId=Fqdc7yjswJv4naJG5KN7kA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>40</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=AEl5xhJHRfxwAuXkc02n7A%3D%3D&amp;trackingId=kjpFnNTkVmgD%2BgUw5rkCBA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Scaled Customer Success ManagerSalesAmericas, New York</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>40</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f6c340cc-7c3f-4706-96c6-07e78dcb1118/scaled-customer-success-manager/</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>40</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=KsHzcOBE4j1My%2F3PM9j3fA%3D%3D&amp;trackingId=JGTl8XCdMYF0b5L2DLVQlg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>VP, Customer Success</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>35</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=9zmm6bwjwW%2BL6NDsuWRkAg%3D%3D&amp;trackingId=7U7Ci9nGDECNIL%2Bjbj7XVg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Commercial Sales Associate</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>25</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=k3afJP%2BL8XgG4b%2BfdDzF%2BQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Product Manager, Payments</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>25</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=7ISJGq2BR4QhXl0Tp7D7hg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Manager, Field Security Specialists (Cyber Solutions Engineering</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>35</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/jobs/view/manager-field-security-specialists-cyber-solutions-engineering-at-openai-4449308650?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=W5gADlCRGJ5aaYSJTSROIQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>JOB-20260806-0227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Ads Solutions (Mumbai)</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>70</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/customer-success-manager-ads-solutions-mumbai-at-openai-4449317487?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=iHg5gALrXxmg4%2FX%2FN4rIkA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -7222,7 +8465,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -7850,8 +9093,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -8132,8 +9375,89 @@
       <c r="F10" t="n">
         <v>28</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:33</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>76</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:42</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>76</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8150,8 +9474,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1026"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E1367"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -31987,6 +33311,7823 @@
       <c r="E1026" t="inlineStr">
         <is>
           <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=N8obzet0IS2NiT5dNqscYw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=J8r8nLy7YGe%2Bfoh2JQ7%2BMA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=S5PbcpiOC9GR7SVXE2zaZg%3D%3D&amp;trackingId=Ms96hphPrllh3LW3Gg4tAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=wOyv7m64G4LcWofHoL26Ag%3D%3D&amp;trackingId=Q0addY%2B7DR6IbHAoGvKNPw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/92e5b670-da4a-4cc3-94ed-740ff37d68df/director-sales-enterprise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/92e5b670-da4a-4cc3-94ed-740ff37d68df/director-sales-enterprise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/76737659-4f27-450f-8f7b-f690723faad5/senior-manager-strategic-partnerships-emea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b2a5c56c-2691-4c4e-b522-5f635ac7d4d5/account-executive-senior-account-executive-enterprise-travel-vertical/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/customer-success-manager-enterprise-at-airwallex-4448014733?refId=BJq1GyANRgi2MTpWYhweXQ%3D%3D&amp;trackingId=LPn453ZuNmxMk%2FEUTZAVFQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=162bByYUJ39qrVdO%2FnKa9Q%3D%3D&amp;trackingId=gjBNN7gBif7eGxC6YGS%2Fng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=vYrn4cTHAhuLiz3lOMTo6Q%3D%3D&amp;trackingId=TIbqVPZ5rPGFtLdzqsAo3A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=4gqmXWpBaou6yWX0%2FnoDrQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=e9kZxmJeV9RCs9NvpdwWVA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://ky.linkedin.com/company/gateofficial/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:00:32</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=TKgG8RBffmQ1EIKmz7f5xA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=H%2B7gh74YvgVeWneRPlvSgA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=raK%2BYE%2B6Zn4NV5U20tR7yQ%3D%3D&amp;trackingId=orMwWTNn5yXw6HVjn%2BnVFQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=%2BVePhyqV1UK7m%2BEpemW%2Bqw%3D%3D&amp;trackingId=MfFMDjXZ7AEFjcm%2BLDClfQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=Eu3zauL8%2BVQYxswknWjyqw%3D%3D&amp;trackingId=jqTc9z9Y%2FhFLbXJptbUyCg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d6a11fda-76e0-439f-ab2f-bbdfd80d9da8/senior-account-executive-enterprise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/8e7e3a2c-c593-49a7-959b-323b7aa57662/account-executive-enterprise-spend-benelux-nordics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/810d3f46-9b64-4d96-85a0-2302658153ba/senior-manager-growth-innovation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/00a7bbce-af16-4d4d-b36b-50034b5d9038/senior-manager-financial-partnerships-apac/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=FhkshE6excHUzWGc6mBoaw%3D%3D&amp;trackingId=LIbaGvcZ2dKomCb9H8QJdg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=ZmDFvJaPiEETvvTPYoCdJA%3D%3D&amp;trackingId=p8GbjFst2c1nAm%2FRSX1TIQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=BrUnoPz20RnN3FATtQcPvw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=VWk%2Bgp3VbNROKLEt%2B94Bhw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/apac-export-lead-ads-solutions-at-openai-4449314412?refId=gRYPAAzUH306VeNbRdZfPA%3D%3D&amp;trackingId=Ja4zQEB%2BpuSFiODzbUgtvw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:05:08</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=TWU%2FE1Gu57Xywn4UfRn0ng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=%2BhAShAezY95tBh3RyiIvfQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=42LfBSOufBhvYUAOL7Y9gw%3D%3D&amp;trackingId=4HSiuDEF191PdMumcLWYLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=aK3Yk7SO5lStab1R44KsRw%3D%3D&amp;trackingId=Fqdc7yjswJv4naJG5KN7kA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=AEl5xhJHRfxwAuXkc02n7A%3D%3D&amp;trackingId=kjpFnNTkVmgD%2BgUw5rkCBA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/741af157-0000-4097-b13c-1e4677a7db49/director-channel-partnerships-sme-growth-americas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f22a8795-d79c-4b80-8e92-92f724d3d23f/manager-growth-strategy-operations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f6c340cc-7c3f-4706-96c6-07e78dcb1118/scaled-customer-success-manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=KsHzcOBE4j1My%2F3PM9j3fA%3D%3D&amp;trackingId=JGTl8XCdMYF0b5L2DLVQlg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=9zmm6bwjwW%2BL6NDsuWRkAg%3D%3D&amp;trackingId=7U7Ci9nGDECNIL%2Bjbj7XVg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=k3afJP%2BL8XgG4b%2BfdDzF%2BQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=7ISJGq2BR4QhXl0Tp7D7hg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/jobs/view/manager-field-security-specialists-cyber-solutions-engineering-at-openai-4449308650?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=W5gADlCRGJ5aaYSJTSROIQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/customer-success-manager-ads-solutions-mumbai-at-openai-4449317487?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=iHg5gALrXxmg4%2FX%2FN4rIkA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-08-06 17:23:41</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
         </is>
       </c>
     </row>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,33 +13,23 @@
     <sheet name="Run_Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,13 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -430,8 +420,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L228"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <dimension ref="A1:L193"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -521,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -556,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -626,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -661,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -696,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -836,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -976,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1011,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1046,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1081,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1116,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1151,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1186,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1361,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1396,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:08</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1571,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1641,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1676,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1711,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1781,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1816,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2118,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Fuzhou</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Chongqing</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2131,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2236,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2271,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2446,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2481,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2516,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2551,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2586,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2621,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2761,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2796,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2831,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2866,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2901,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2936,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2971,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3006,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3041,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3076,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3111,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3146,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3181,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3216,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3251,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3286,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3321,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3356,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3391,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3426,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3461,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3496,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3531,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3566,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3601,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3636,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3671,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3706,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4196,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4231,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5491,7 +5481,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -5526,7 +5516,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5561,7 +5551,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:08</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5701,7 +5691,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -6248,7 +6238,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Director, Sales, EnterpriseSalesSales•New YorkAmericas,New YorkNew York</t>
+          <t>Director, Sales, EnterpriseSalesSales•San FranciscoAmericas,San FranciscoSan Francisco</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -6261,7 +6251,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-08-06 17:00:32</t>
+          <t>2026-08-05 17:06:50</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -6703,7 +6693,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Manager, Growth Strategy &amp; OperationsOperations ManagementAPAC, Singapore</t>
+          <t>Manager, Growth Strategy &amp; OperationsOperations ManagementOperations Management•SingaporeAPAC,SingaporeSingapore</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -6716,7 +6706,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -6738,7 +6728,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Senior Account Executive, EnterpriseSalesSales•MelbourneAPAC,MelbourneMelbourne</t>
+          <t>Senior Account Executive, EnterpriseSalesAPAC, Melbourne</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -6751,7 +6741,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:08</t>
+          <t>2026-08-05 17:35:46</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -6926,7 +6916,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -6961,7 +6951,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-08-06 17:00:32</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -7101,7 +7091,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7136,7 +7126,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-06 17:23:41</t>
+          <t>2026-08-06 08:52:31</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -7210,1239 +7200,6 @@
         </is>
       </c>
       <c r="J193" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0193</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Program Manager, Commercial Solutions</t>
-        </is>
-      </c>
-      <c r="F194" t="n">
-        <v>75</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=N8obzet0IS2NiT5dNqscYw%3D%3D</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0194</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Risk Operations Program Manager</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
-        <v>40</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=J8r8nLy7YGe%2Bfoh2JQ7%2BMA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0195</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Business Analyst - Operations</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>25</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=S5PbcpiOC9GR7SVXE2zaZg%3D%3D&amp;trackingId=Ms96hphPrllh3LW3Gg4tAQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0196</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Payoneer</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Senior Business Development Manager</t>
-        </is>
-      </c>
-      <c r="F197" t="n">
-        <v>40</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=wOyv7m64G4LcWofHoL26Ag%3D%3D&amp;trackingId=Q0addY%2B7DR6IbHAoGvKNPw%3D%3D</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0197</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Account Executive/Senior Account Executive, Enterprise (Travel Vertical)SalesAPAC, Jakarta</t>
-        </is>
-      </c>
-      <c r="F198" t="n">
-        <v>45</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/b2a5c56c-2691-4c4e-b522-5f635ac7d4d5/account-executive-senior-account-executive-enterprise-travel-vertical/</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0198</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Customer Success Manager, Enterprise</t>
-        </is>
-      </c>
-      <c r="F199" t="n">
-        <v>55</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://hk.linkedin.com/jobs/view/customer-success-manager-enterprise-at-airwallex-4448014733?refId=BJq1GyANRgi2MTpWYhweXQ%3D%3D&amp;trackingId=LPn453ZuNmxMk%2FEUTZAVFQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0199</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Business Development Manager- Mexico</t>
-        </is>
-      </c>
-      <c r="F200" t="n">
-        <v>40</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=162bByYUJ39qrVdO%2FnKa9Q%3D%3D&amp;trackingId=gjBNN7gBif7eGxC6YGS%2Fng%3D%3D</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0200</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>VP, Customer Success</t>
-        </is>
-      </c>
-      <c r="F201" t="n">
-        <v>35</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=vYrn4cTHAhuLiz3lOMTo6Q%3D%3D&amp;trackingId=TIbqVPZ5rPGFtLdzqsAo3A%3D%3D</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0201</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Commercial Sales Associate</t>
-        </is>
-      </c>
-      <c r="F202" t="n">
-        <v>25</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=4gqmXWpBaou6yWX0%2FnoDrQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0202</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Product Manager, Payments</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>25</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=e9kZxmJeV9RCs9NvpdwWVA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0203</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Program Manager, Commercial Solutions</t>
-        </is>
-      </c>
-      <c r="F204" t="n">
-        <v>75</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=TKgG8RBffmQ1EIKmz7f5xA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="K204" s="2" t="n">
-        <v>46240</v>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0204</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Risk Operations Program Manager</t>
-        </is>
-      </c>
-      <c r="F205" t="n">
-        <v>40</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=H%2B7gh74YvgVeWneRPlvSgA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0205</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Business Analyst - Operations</t>
-        </is>
-      </c>
-      <c r="F206" t="n">
-        <v>25</v>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=raK%2BYE%2B6Zn4NV5U20tR7yQ%3D%3D&amp;trackingId=orMwWTNn5yXw6HVjn%2BnVFQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0206</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Business Development Manager</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
-        <v>40</v>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=%2BVePhyqV1UK7m%2BEpemW%2Bqw%3D%3D&amp;trackingId=MfFMDjXZ7AEFjcm%2BLDClfQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0207</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Payoneer</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Senior Business Development Manager</t>
-        </is>
-      </c>
-      <c r="F208" t="n">
-        <v>40</v>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=Eu3zauL8%2BVQYxswknWjyqw%3D%3D&amp;trackingId=jqTc9z9Y%2FhFLbXJptbUyCg%3D%3D</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0208</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Account Executive, Enterprise Spend – Benelux &amp; NordicsSalesAmsterdam, EMEA</t>
-        </is>
-      </c>
-      <c r="F209" t="n">
-        <v>45</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/8e7e3a2c-c593-49a7-959b-323b7aa57662/account-executive-enterprise-spend-benelux-nordics/</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0209</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Senior Manager, Growth InnovationOperations ManagementAmericas, San Francisco</t>
-        </is>
-      </c>
-      <c r="F210" t="n">
-        <v>25</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/810d3f46-9b64-4d96-85a0-2302658153ba/senior-manager-growth-innovation/</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0210</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Senior Manager, Financial Partnerships APACFinancial and Strategic PartnershipsAPAC, Sydney</t>
-        </is>
-      </c>
-      <c r="F211" t="n">
-        <v>45</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/00a7bbce-af16-4d4d-b36b-50034b5d9038/senior-manager-financial-partnerships-apac/</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0211</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Business Development Manager- Mexico</t>
-        </is>
-      </c>
-      <c r="F212" t="n">
-        <v>40</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=FhkshE6excHUzWGc6mBoaw%3D%3D&amp;trackingId=LIbaGvcZ2dKomCb9H8QJdg%3D%3D</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0212</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>VP, Customer Success</t>
-        </is>
-      </c>
-      <c r="F213" t="n">
-        <v>35</v>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=ZmDFvJaPiEETvvTPYoCdJA%3D%3D&amp;trackingId=p8GbjFst2c1nAm%2FRSX1TIQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0213</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Commercial Sales Associate</t>
-        </is>
-      </c>
-      <c r="F214" t="n">
-        <v>25</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=BrUnoPz20RnN3FATtQcPvw%3D%3D</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0214</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Product Manager, Payments</t>
-        </is>
-      </c>
-      <c r="F215" t="n">
-        <v>25</v>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=VWk%2Bgp3VbNROKLEt%2B94Bhw%3D%3D</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0215</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>APAC Export Lead, Ads Solutions</t>
-        </is>
-      </c>
-      <c r="F216" t="n">
-        <v>35</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/apac-export-lead-ads-solutions-at-openai-4449314412?refId=gRYPAAzUH306VeNbRdZfPA%3D%3D&amp;trackingId=Ja4zQEB%2BpuSFiODzbUgtvw%3D%3D</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0216</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Program Manager, Commercial Solutions</t>
-        </is>
-      </c>
-      <c r="F217" t="n">
-        <v>75</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=TWU%2FE1Gu57Xywn4UfRn0ng%3D%3D</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0217</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Risk Operations Program Manager</t>
-        </is>
-      </c>
-      <c r="F218" t="n">
-        <v>40</v>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=%2BhAShAezY95tBh3RyiIvfQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0218</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Business Analyst - Operations</t>
-        </is>
-      </c>
-      <c r="F219" t="n">
-        <v>25</v>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=42LfBSOufBhvYUAOL7Y9gw%3D%3D&amp;trackingId=4HSiuDEF191PdMumcLWYLw%3D%3D</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0219</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Business Development Manager</t>
-        </is>
-      </c>
-      <c r="F220" t="n">
-        <v>40</v>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=aK3Yk7SO5lStab1R44KsRw%3D%3D&amp;trackingId=Fqdc7yjswJv4naJG5KN7kA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0220</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Payoneer</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Senior Business Development Manager</t>
-        </is>
-      </c>
-      <c r="F221" t="n">
-        <v>40</v>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=AEl5xhJHRfxwAuXkc02n7A%3D%3D&amp;trackingId=kjpFnNTkVmgD%2BgUw5rkCBA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0221</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Scaled Customer Success ManagerSalesAmericas, New York</t>
-        </is>
-      </c>
-      <c r="F222" t="n">
-        <v>40</v>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/f6c340cc-7c3f-4706-96c6-07e78dcb1118/scaled-customer-success-manager/</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0222</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Business Development Manager- Mexico</t>
-        </is>
-      </c>
-      <c r="F223" t="n">
-        <v>40</v>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=KsHzcOBE4j1My%2F3PM9j3fA%3D%3D&amp;trackingId=JGTl8XCdMYF0b5L2DLVQlg%3D%3D</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0223</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>VP, Customer Success</t>
-        </is>
-      </c>
-      <c r="F224" t="n">
-        <v>35</v>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=9zmm6bwjwW%2BL6NDsuWRkAg%3D%3D&amp;trackingId=7U7Ci9nGDECNIL%2Bjbj7XVg%3D%3D</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0224</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Commercial Sales Associate</t>
-        </is>
-      </c>
-      <c r="F225" t="n">
-        <v>25</v>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=k3afJP%2BL8XgG4b%2BfdDzF%2BQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0225</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Product Manager, Payments</t>
-        </is>
-      </c>
-      <c r="F226" t="n">
-        <v>25</v>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=7ISJGq2BR4QhXl0Tp7D7hg%3D%3D</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0226</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Manager, Field Security Specialists (Cyber Solutions Engineering</t>
-        </is>
-      </c>
-      <c r="F227" t="n">
-        <v>35</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://ie.linkedin.com/jobs/view/manager-field-security-specialists-cyber-solutions-engineering-at-openai-4449308650?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=W5gADlCRGJ5aaYSJTSROIQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>JOB-20260806-0227</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Customer Success Manager, Ads Solutions (Mumbai)</t>
-        </is>
-      </c>
-      <c r="F228" t="n">
-        <v>70</v>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://in.linkedin.com/jobs/view/customer-success-manager-ads-solutions-mumbai-at-openai-4449317487?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=iHg5gALrXxmg4%2FX%2FN4rIkA%3D%3D</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -8465,7 +7222,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -9093,8 +7850,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -9375,89 +8132,8 @@
       <c r="F10" t="n">
         <v>28</v>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:33</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>76</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:09</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>76</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:42</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>76</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>17</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9474,8 +8150,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1367"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <dimension ref="A1:E1026"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -33311,7823 +31987,6 @@
       <c r="E1026" t="inlineStr">
         <is>
           <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise</t>
-        </is>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1027" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1027" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1027" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
-        </is>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1028" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1028" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1028" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
-        </is>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1029" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1029" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1029" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
-        </is>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1030" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1030" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1030" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
-        </is>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1031" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1031" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1031" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
-        </is>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1032" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1032" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1032" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
-        </is>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1033" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1033" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1033" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=N8obzet0IS2NiT5dNqscYw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1034" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1034" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1034" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=TaZqHcpIOQ9OejzdVvgcSQ%3D%3D&amp;trackingId=J8r8nLy7YGe%2Bfoh2JQ7%2BMA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1035" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1035" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="D1035" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=S5PbcpiOC9GR7SVXE2zaZg%3D%3D&amp;trackingId=Ms96hphPrllh3LW3Gg4tAQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1036" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1037" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1037" t="inlineStr">
-        <is>
-          <t>Payoneer</t>
-        </is>
-      </c>
-      <c r="D1037" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=wOyv7m64G4LcWofHoL26Ag%3D%3D&amp;trackingId=Q0addY%2B7DR6IbHAoGvKNPw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1038" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1038" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/92e5b670-da4a-4cc3-94ed-740ff37d68df/director-sales-enterprise/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1039" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/92e5b670-da4a-4cc3-94ed-740ff37d68df/director-sales-enterprise/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1040" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/76737659-4f27-450f-8f7b-f690723faad5/senior-manager-strategic-partnerships-emea/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1041" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/b2a5c56c-2691-4c4e-b522-5f635ac7d4d5/account-executive-senior-account-executive-enterprise-travel-vertical/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1042" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1043" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1044" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1044" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1044" t="inlineStr">
-        <is>
-          <t>https://hk.linkedin.com/jobs/view/customer-success-manager-enterprise-at-airwallex-4448014733?refId=BJq1GyANRgi2MTpWYhweXQ%3D%3D&amp;trackingId=LPn453ZuNmxMk%2FEUTZAVFQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1045" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1045" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1045" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
-        </is>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1046" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1046" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1046" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1047" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1047" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1047" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1048" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1048" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
-        </is>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1049" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1049" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1049" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1050" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1050" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1050" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1051" t="inlineStr">
-        <is>
-          <t>Checkout.com</t>
-        </is>
-      </c>
-      <c r="D1051" t="inlineStr">
-        <is>
-          <t>https://www.checkout.com/products/payment-links</t>
-        </is>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1052" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1052" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1052" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/payment-solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1053" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1053" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1053" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/online-retail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1054" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1054" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
-        </is>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1055" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1055" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1055" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
-        </is>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1056" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1056" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1056" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
-        </is>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1057" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1057" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1057" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1058" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1058" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1059" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1059" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1060" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1060" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1060" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1061" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1061" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1061" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/issuing</t>
-        </is>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1062" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1062" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1062" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/apm</t>
-        </is>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1063" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1063" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1063" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/real-time-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1064" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1064" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1064" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/bank-transfers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1065" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1065" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1065" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1066" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1066" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1066" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
-        </is>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1067" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1067" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1067" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1068" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1068" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1068" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/currency-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1069" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1069" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1069" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1070" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1070" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1070" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
-        </is>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1071" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1071" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1071" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1072" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1072" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1072" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/hospitality</t>
-        </is>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1073" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1073" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1073" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/automotive</t>
-        </is>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1074" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1074" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1074" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/grocery</t>
-        </is>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1075" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1075" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1075" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1076" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1076" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1076" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
-        </is>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1077" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1077" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1077" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
-        </is>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1078" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1078" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1078" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/business-to-business</t>
-        </is>
-      </c>
-    </row>
-    <row r="1079">
-      <c r="A1079" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1079" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1079" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1079" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
-        </is>
-      </c>
-    </row>
-    <row r="1080">
-      <c r="A1080" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1080" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1080" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1080" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/online-gaming</t>
-        </is>
-      </c>
-    </row>
-    <row r="1081">
-      <c r="A1081" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1081" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1081" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1081" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="1082">
-      <c r="A1082" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1082" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1082" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1082" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1083">
-      <c r="A1083" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1083" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1083" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1083" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="1084">
-      <c r="A1084" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1084" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1084" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1084" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1085" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1085" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1085" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1086" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1086" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1086" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1087" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1087" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1087" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1088" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1088" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1088" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=162bByYUJ39qrVdO%2FnKa9Q%3D%3D&amp;trackingId=gjBNN7gBif7eGxC6YGS%2Fng%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1089" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1089" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1089" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1090" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1090" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1090" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1091" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1091" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1091" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1092" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1092" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1092" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1093" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1093" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1093" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1094" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1094" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1094" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=vYrn4cTHAhuLiz3lOMTo6Q%3D%3D&amp;trackingId=TIbqVPZ5rPGFtLdzqsAo3A%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1095">
-      <c r="A1095" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1095" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1095" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1095" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1096">
-      <c r="A1096" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1096" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1096" t="inlineStr">
-        <is>
-          <t>Ripple</t>
-        </is>
-      </c>
-      <c r="D1096" t="inlineStr">
-        <is>
-          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1097" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1097" t="inlineStr">
-        <is>
-          <t>Ripple</t>
-        </is>
-      </c>
-      <c r="D1097" t="inlineStr">
-        <is>
-          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1098" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1098" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="D1098" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1099" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1099" t="inlineStr">
-        <is>
-          <t>BVNK</t>
-        </is>
-      </c>
-      <c r="D1099" t="inlineStr">
-        <is>
-          <t>https://www.bvnk.com/self-managed-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1100" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1100" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1100" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1101" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1101" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1101" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1102" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1102" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1102" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1103" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1103" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1103" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1104" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1104" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1104" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1105" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1105" t="inlineStr">
-        <is>
-          <t>Triple-A</t>
-        </is>
-      </c>
-      <c r="D1105" t="inlineStr">
-        <is>
-          <t>https://triple-a.io/case-studies</t>
-        </is>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1106" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1106" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1106" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=4gqmXWpBaou6yWX0%2FnoDrQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1107" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1107" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1107" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=sBCuq%2FRhBOhmOuJlhZzpxw%3D%3D&amp;trackingId=e9kZxmJeV9RCs9NvpdwWVA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1108" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1108" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1108" t="inlineStr">
-        <is>
-          <t>https://unlimit.com/ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="1109">
-      <c r="A1109" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1109" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1109" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1109" t="inlineStr">
-        <is>
-          <t>https://unlimit.com/ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="1110">
-      <c r="A1110" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1110" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1110" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1110" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
-        </is>
-      </c>
-    </row>
-    <row r="1111">
-      <c r="A1111" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1111" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1111" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1111" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
-        </is>
-      </c>
-    </row>
-    <row r="1112">
-      <c r="A1112" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1112" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1112" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1112" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
-        </is>
-      </c>
-    </row>
-    <row r="1113">
-      <c r="A1113" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1113" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1113" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1113" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
-        </is>
-      </c>
-    </row>
-    <row r="1114">
-      <c r="A1114" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1114" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1114" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1114" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1115">
-      <c r="A1115" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1115" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1115" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1115" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1116">
-      <c r="A1116" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1116" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1116" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1116" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1117">
-      <c r="A1117" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1117" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1117" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1117" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1118">
-      <c r="A1118" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1118" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1118" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1118" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/wise-platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="1119">
-      <c r="A1119" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1119" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1119" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1119" t="inlineStr">
-        <is>
-          <t>https://jobs.visa.com/</t>
-        </is>
-      </c>
-      <c r="E1119" t="inlineStr">
-        <is>
-          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
-        </is>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1120" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1120" t="inlineStr">
-        <is>
-          <t>Checkout.com</t>
-        </is>
-      </c>
-      <c r="D1120" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
-        </is>
-      </c>
-      <c r="E1120" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1121" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1121" t="inlineStr">
-        <is>
-          <t>Thunes</t>
-        </is>
-      </c>
-      <c r="D1121" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/thunes/jobs/</t>
-        </is>
-      </c>
-      <c r="E1121" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1122">
-      <c r="A1122" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1122" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1122" t="inlineStr">
-        <is>
-          <t>Rapyd</t>
-        </is>
-      </c>
-      <c r="D1122" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
-        </is>
-      </c>
-      <c r="E1122" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1123">
-      <c r="A1123" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1123" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1123" t="inlineStr">
-        <is>
-          <t>Circle</t>
-        </is>
-      </c>
-      <c r="D1123" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/circle/jobs/</t>
-        </is>
-      </c>
-      <c r="E1123" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1124">
-      <c r="A1124" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1124" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1124" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1124" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
-        </is>
-      </c>
-      <c r="E1124" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1125">
-      <c r="A1125" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1125" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1125" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1125" t="inlineStr">
-        <is>
-          <t>https://www.straitsx.com/careers</t>
-        </is>
-      </c>
-      <c r="E1125" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1126">
-      <c r="A1126" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1126" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1126" t="inlineStr">
-        <is>
-          <t>OSL</t>
-        </is>
-      </c>
-      <c r="D1126" t="inlineStr">
-        <is>
-          <t>https://osl.com/careers/</t>
-        </is>
-      </c>
-      <c r="E1126" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1127">
-      <c r="A1127" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1127" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1127" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1127" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
-        </is>
-      </c>
-      <c r="E1127" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1128">
-      <c r="A1128" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1128" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1128" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="D1128" t="inlineStr">
-        <is>
-          <t>https://www.okx.com/careers</t>
-        </is>
-      </c>
-      <c r="E1128" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1129">
-      <c r="A1129" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1129" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1129" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="D1129" t="inlineStr">
-        <is>
-          <t>https://www.gate.io/careers</t>
-        </is>
-      </c>
-      <c r="E1129" t="inlineStr">
-        <is>
-          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1130">
-      <c r="A1130" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1130" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1130" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="D1130" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/gateio/jobs/</t>
-        </is>
-      </c>
-      <c r="E1130" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://ky.linkedin.com/company/gateofficial/jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1131">
-      <c r="A1131" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1131" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1131" t="inlineStr">
-        <is>
-          <t>Reap</t>
-        </is>
-      </c>
-      <c r="D1131" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
-        </is>
-      </c>
-      <c r="E1131" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1132">
-      <c r="A1132" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1132" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1132" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="D1132" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-      <c r="E1132" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1133">
-      <c r="A1133" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1133" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1133" t="inlineStr">
-        <is>
-          <t>MiniMax</t>
-        </is>
-      </c>
-      <c r="D1133" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
-        </is>
-      </c>
-      <c r="E1133" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="1134">
-      <c r="A1134" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1134" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1134" t="inlineStr">
-        <is>
-          <t>Skyfire</t>
-        </is>
-      </c>
-      <c r="D1134" t="inlineStr">
-        <is>
-          <t>https://www.skyfire.xyz/careers</t>
-        </is>
-      </c>
-      <c r="E1134" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1135">
-      <c r="A1135" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1135" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1135" t="inlineStr">
-        <is>
-          <t>Skyfire</t>
-        </is>
-      </c>
-      <c r="D1135" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-      <c r="E1135" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1136">
-      <c r="A1136" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1136" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1136" t="inlineStr">
-        <is>
-          <t>Nevermined</t>
-        </is>
-      </c>
-      <c r="D1136" t="inlineStr">
-        <is>
-          <t>https://nevermined.io/careers</t>
-        </is>
-      </c>
-      <c r="E1136" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1137">
-      <c r="A1137" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1137" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1137" t="inlineStr">
-        <is>
-          <t>Nevermined</t>
-        </is>
-      </c>
-      <c r="D1137" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
-        </is>
-      </c>
-      <c r="E1137" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
-        </is>
-      </c>
-    </row>
-    <row r="1138">
-      <c r="A1138" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1138" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1138" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D1138" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/openai/jobs/</t>
-        </is>
-      </c>
-      <c r="E1138" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1139">
-      <c r="A1139" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1139" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1139" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D1139" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
-        </is>
-      </c>
-      <c r="E1139" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic</t>
-        </is>
-      </c>
-    </row>
-    <row r="1140">
-      <c r="A1140" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:00:32</t>
-        </is>
-      </c>
-      <c r="B1140" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1140" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="D1140" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
-        </is>
-      </c>
-      <c r="E1140" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1141">
-      <c r="A1141" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1141" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1141" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1141" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
-        </is>
-      </c>
-    </row>
-    <row r="1142">
-      <c r="A1142" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1142" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1142" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1142" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
-        </is>
-      </c>
-    </row>
-    <row r="1143">
-      <c r="A1143" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1143" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1143" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1143" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
-        </is>
-      </c>
-    </row>
-    <row r="1144">
-      <c r="A1144" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1144" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1144" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1144" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
-        </is>
-      </c>
-    </row>
-    <row r="1145">
-      <c r="A1145" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1145" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1145" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1145" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
-        </is>
-      </c>
-    </row>
-    <row r="1146">
-      <c r="A1146" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1146" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1146" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1146" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
-        </is>
-      </c>
-    </row>
-    <row r="1147">
-      <c r="A1147" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1147" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1147" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1147" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=TKgG8RBffmQ1EIKmz7f5xA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1148">
-      <c r="A1148" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1148" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1148" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1148" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=qaoECyjSQQ%2FR2fOWxjTPFA%3D%3D&amp;trackingId=H%2B7gh74YvgVeWneRPlvSgA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1149">
-      <c r="A1149" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1149" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1149" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="D1149" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=raK%2BYE%2B6Zn4NV5U20tR7yQ%3D%3D&amp;trackingId=orMwWTNn5yXw6HVjn%2BnVFQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1150">
-      <c r="A1150" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1150" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1150" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1150" t="inlineStr">
-        <is>
-          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=%2BVePhyqV1UK7m%2BEpemW%2Bqw%3D%3D&amp;trackingId=MfFMDjXZ7AEFjcm%2BLDClfQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1151">
-      <c r="A1151" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1151" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1151" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1151" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="1152">
-      <c r="A1152" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1152" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1152" t="inlineStr">
-        <is>
-          <t>Payoneer</t>
-        </is>
-      </c>
-      <c r="D1152" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=Eu3zauL8%2BVQYxswknWjyqw%3D%3D&amp;trackingId=jqTc9z9Y%2FhFLbXJptbUyCg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1153">
-      <c r="A1153" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1153" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1153" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1153" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/d6a11fda-76e0-439f-ab2f-bbdfd80d9da8/senior-account-executive-enterprise/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1154">
-      <c r="A1154" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1154" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1154" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1154" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/8e7e3a2c-c593-49a7-959b-323b7aa57662/account-executive-enterprise-spend-benelux-nordics/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1155">
-      <c r="A1155" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1155" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1155" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1155" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/810d3f46-9b64-4d96-85a0-2302658153ba/senior-manager-growth-innovation/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1156">
-      <c r="A1156" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1156" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1156" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1156" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/00a7bbce-af16-4d4d-b36b-50034b5d9038/senior-manager-financial-partnerships-apac/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1157" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1157" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1157" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1158" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1158" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1158" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1159" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1159" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1159" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
-        </is>
-      </c>
-    </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1160" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1160" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1160" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1161" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1161" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1161" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1162" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1162" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1162" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
-        </is>
-      </c>
-    </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1163" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1163" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1163" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1164" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1164" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1164" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1165" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1165" t="inlineStr">
-        <is>
-          <t>Checkout.com</t>
-        </is>
-      </c>
-      <c r="D1165" t="inlineStr">
-        <is>
-          <t>https://www.checkout.com/products/payment-links</t>
-        </is>
-      </c>
-    </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1166" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1166" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1166" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/payment-solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1167" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1167" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1167" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/online-retail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1168" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1168" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1168" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
-        </is>
-      </c>
-    </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1169" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1169" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1169" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
-        </is>
-      </c>
-    </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1170" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1170" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1170" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
-        </is>
-      </c>
-    </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1171" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1171" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1171" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1172" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1172" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1172" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1173" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1173" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1173" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1174" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1174" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1174" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1175" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1175" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1175" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/issuing</t>
-        </is>
-      </c>
-    </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1176" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1176" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1176" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/apm</t>
-        </is>
-      </c>
-    </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1177" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1177" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1177" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/real-time-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1178" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1178" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1178" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/bank-transfers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1179" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1179" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1179" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1180" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1180" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1180" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
-        </is>
-      </c>
-    </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1181" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1181" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1181" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1182" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1182" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1182" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/currency-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1183" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1183" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1183" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1184" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1184" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1184" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
-        </is>
-      </c>
-    </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1185" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1185" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1185" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1186" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1186" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1186" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/hospitality</t>
-        </is>
-      </c>
-    </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1187" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1187" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1187" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/automotive</t>
-        </is>
-      </c>
-    </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1188" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1188" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1188" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/grocery</t>
-        </is>
-      </c>
-    </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1189" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1189" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1189" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1190" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1190" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1190" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
-        </is>
-      </c>
-    </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1191" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1191" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1191" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
-        </is>
-      </c>
-    </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1192" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1192" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1192" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/business-to-business</t>
-        </is>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1193" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1193" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1193" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
-        </is>
-      </c>
-    </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1194" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1194" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1194" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/online-gaming</t>
-        </is>
-      </c>
-    </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1195" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1195" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1195" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1196" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1196" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1196" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1197" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1197" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1197" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1198" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1198" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1198" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1199" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1199" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1199" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1200" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1200" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1200" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1201" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1201" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1201" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1202" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1202" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1202" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=FhkshE6excHUzWGc6mBoaw%3D%3D&amp;trackingId=LIbaGvcZ2dKomCb9H8QJdg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1203" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1203" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1203" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1204" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1204" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1204" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1205" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1205" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1205" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1206" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1206" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1206" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1207" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1207" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1207" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1208" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1208" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1208" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=ZmDFvJaPiEETvvTPYoCdJA%3D%3D&amp;trackingId=p8GbjFst2c1nAm%2FRSX1TIQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1209" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1209" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1209" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1210" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1210" t="inlineStr">
-        <is>
-          <t>Ripple</t>
-        </is>
-      </c>
-      <c r="D1210" t="inlineStr">
-        <is>
-          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1211">
-      <c r="A1211" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1211" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1211" t="inlineStr">
-        <is>
-          <t>Ripple</t>
-        </is>
-      </c>
-      <c r="D1211" t="inlineStr">
-        <is>
-          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1212">
-      <c r="A1212" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1212" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1212" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="D1212" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1213">
-      <c r="A1213" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1213" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1213" t="inlineStr">
-        <is>
-          <t>BVNK</t>
-        </is>
-      </c>
-      <c r="D1213" t="inlineStr">
-        <is>
-          <t>https://www.bvnk.com/self-managed-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1214">
-      <c r="A1214" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1214" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1214" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1214" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1215">
-      <c r="A1215" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1215" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1215" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1215" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1216">
-      <c r="A1216" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1216" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1216" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1216" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1217">
-      <c r="A1217" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1217" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1217" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1217" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1218">
-      <c r="A1218" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1218" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1218" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1218" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1219">
-      <c r="A1219" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1219" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1219" t="inlineStr">
-        <is>
-          <t>Triple-A</t>
-        </is>
-      </c>
-      <c r="D1219" t="inlineStr">
-        <is>
-          <t>https://triple-a.io/case-studies</t>
-        </is>
-      </c>
-    </row>
-    <row r="1220">
-      <c r="A1220" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1220" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1220" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1220" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=BrUnoPz20RnN3FATtQcPvw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1221">
-      <c r="A1221" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1221" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1221" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1221" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=k3TuhnwpakEUpZF9i%2Fbu0Q%3D%3D&amp;trackingId=VWk%2Bgp3VbNROKLEt%2B94Bhw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1222">
-      <c r="A1222" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1222" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1222" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1222" t="inlineStr">
-        <is>
-          <t>https://unlimit.com/ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="1223">
-      <c r="A1223" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1223" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1223" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1223" t="inlineStr">
-        <is>
-          <t>https://unlimit.com/ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="1224">
-      <c r="A1224" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1224" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1224" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1224" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
-        </is>
-      </c>
-    </row>
-    <row r="1225">
-      <c r="A1225" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1225" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1225" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1225" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
-        </is>
-      </c>
-    </row>
-    <row r="1226">
-      <c r="A1226" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1226" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1226" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1226" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
-        </is>
-      </c>
-    </row>
-    <row r="1227">
-      <c r="A1227" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1227" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1227" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1227" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
-        </is>
-      </c>
-    </row>
-    <row r="1228">
-      <c r="A1228" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1228" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1228" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D1228" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/apac-export-lead-ads-solutions-at-openai-4449314412?refId=gRYPAAzUH306VeNbRdZfPA%3D%3D&amp;trackingId=Ja4zQEB%2BpuSFiODzbUgtvw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1229">
-      <c r="A1229" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1229" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1229" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1229" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1230">
-      <c r="A1230" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1230" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1230" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1230" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1231">
-      <c r="A1231" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1231" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1231" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1231" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1232">
-      <c r="A1232" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1232" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1232" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1232" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1233">
-      <c r="A1233" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1233" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1233" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1233" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/wise-platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="1234">
-      <c r="A1234" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1234" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1234" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1234" t="inlineStr">
-        <is>
-          <t>https://jobs.visa.com/</t>
-        </is>
-      </c>
-      <c r="E1234" t="inlineStr">
-        <is>
-          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
-        </is>
-      </c>
-    </row>
-    <row r="1235">
-      <c r="A1235" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1235" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1235" t="inlineStr">
-        <is>
-          <t>Checkout.com</t>
-        </is>
-      </c>
-      <c r="D1235" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
-        </is>
-      </c>
-      <c r="E1235" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1236">
-      <c r="A1236" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1236" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1236" t="inlineStr">
-        <is>
-          <t>Thunes</t>
-        </is>
-      </c>
-      <c r="D1236" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/thunes/jobs/</t>
-        </is>
-      </c>
-      <c r="E1236" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1237">
-      <c r="A1237" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1237" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1237" t="inlineStr">
-        <is>
-          <t>Rapyd</t>
-        </is>
-      </c>
-      <c r="D1237" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
-        </is>
-      </c>
-      <c r="E1237" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1238">
-      <c r="A1238" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1238" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1238" t="inlineStr">
-        <is>
-          <t>Circle</t>
-        </is>
-      </c>
-      <c r="D1238" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/circle/jobs/</t>
-        </is>
-      </c>
-      <c r="E1238" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1239">
-      <c r="A1239" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1239" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1239" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1239" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
-        </is>
-      </c>
-      <c r="E1239" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1240">
-      <c r="A1240" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1240" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1240" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1240" t="inlineStr">
-        <is>
-          <t>https://www.straitsx.com/careers</t>
-        </is>
-      </c>
-      <c r="E1240" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1241">
-      <c r="A1241" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1241" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1241" t="inlineStr">
-        <is>
-          <t>OSL</t>
-        </is>
-      </c>
-      <c r="D1241" t="inlineStr">
-        <is>
-          <t>https://osl.com/careers/</t>
-        </is>
-      </c>
-      <c r="E1241" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1242">
-      <c r="A1242" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1242" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1242" t="inlineStr">
-        <is>
-          <t>OSL</t>
-        </is>
-      </c>
-      <c r="D1242" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
-        </is>
-      </c>
-      <c r="E1242" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1243">
-      <c r="A1243" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1243" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1243" t="inlineStr">
-        <is>
-          <t>Tazapay</t>
-        </is>
-      </c>
-      <c r="D1243" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
-        </is>
-      </c>
-      <c r="E1243" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1244">
-      <c r="A1244" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1244" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1244" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1244" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
-        </is>
-      </c>
-      <c r="E1244" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1245">
-      <c r="A1245" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1245" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1245" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="D1245" t="inlineStr">
-        <is>
-          <t>https://www.okx.com/careers</t>
-        </is>
-      </c>
-      <c r="E1245" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1246">
-      <c r="A1246" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1246" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1246" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="D1246" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/okx/jobs/</t>
-        </is>
-      </c>
-      <c r="E1246" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1247">
-      <c r="A1247" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1247" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1247" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="D1247" t="inlineStr">
-        <is>
-          <t>https://www.gate.io/careers</t>
-        </is>
-      </c>
-      <c r="E1247" t="inlineStr">
-        <is>
-          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1248">
-      <c r="A1248" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1248" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1248" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="D1248" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/gateio/jobs/</t>
-        </is>
-      </c>
-      <c r="E1248" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1249">
-      <c r="A1249" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1249" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1249" t="inlineStr">
-        <is>
-          <t>Reap</t>
-        </is>
-      </c>
-      <c r="D1249" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
-        </is>
-      </c>
-      <c r="E1249" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1250">
-      <c r="A1250" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1250" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1250" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="D1250" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-      <c r="E1250" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1251">
-      <c r="A1251" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1251" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1251" t="inlineStr">
-        <is>
-          <t>MiniMax</t>
-        </is>
-      </c>
-      <c r="D1251" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
-        </is>
-      </c>
-      <c r="E1251" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="1252">
-      <c r="A1252" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1252" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1252" t="inlineStr">
-        <is>
-          <t>Skyfire</t>
-        </is>
-      </c>
-      <c r="D1252" t="inlineStr">
-        <is>
-          <t>https://www.skyfire.xyz/careers</t>
-        </is>
-      </c>
-      <c r="E1252" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1253">
-      <c r="A1253" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1253" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1253" t="inlineStr">
-        <is>
-          <t>Skyfire</t>
-        </is>
-      </c>
-      <c r="D1253" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-      <c r="E1253" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1254">
-      <c r="A1254" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1254" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1254" t="inlineStr">
-        <is>
-          <t>Nevermined</t>
-        </is>
-      </c>
-      <c r="D1254" t="inlineStr">
-        <is>
-          <t>https://nevermined.io/careers</t>
-        </is>
-      </c>
-      <c r="E1254" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1255">
-      <c r="A1255" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1255" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1255" t="inlineStr">
-        <is>
-          <t>Nevermined</t>
-        </is>
-      </c>
-      <c r="D1255" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
-        </is>
-      </c>
-      <c r="E1255" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
-        </is>
-      </c>
-    </row>
-    <row r="1256">
-      <c r="A1256" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1256" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1256" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D1256" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
-        </is>
-      </c>
-      <c r="E1256" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic</t>
-        </is>
-      </c>
-    </row>
-    <row r="1257">
-      <c r="A1257" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:05:08</t>
-        </is>
-      </c>
-      <c r="B1257" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1257" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="D1257" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
-        </is>
-      </c>
-      <c r="E1257" t="inlineStr">
-        <is>
-          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1258">
-      <c r="A1258" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1258" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1258" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1258" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
-        </is>
-      </c>
-    </row>
-    <row r="1259">
-      <c r="A1259" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1259" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1259" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1259" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
-        </is>
-      </c>
-    </row>
-    <row r="1260">
-      <c r="A1260" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1260" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1260" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1260" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
-        </is>
-      </c>
-    </row>
-    <row r="1261">
-      <c r="A1261" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1261" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1261" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1261" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
-        </is>
-      </c>
-    </row>
-    <row r="1262">
-      <c r="A1262" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1262" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1262" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1262" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
-        </is>
-      </c>
-    </row>
-    <row r="1263">
-      <c r="A1263" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1263" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1263" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1263" t="inlineStr">
-        <is>
-          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
-        </is>
-      </c>
-    </row>
-    <row r="1264">
-      <c r="A1264" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1264" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1264" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1264" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/program-manager-commercial-solutions-at-stripe-4425913167?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=TWU%2FE1Gu57Xywn4UfRn0ng%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1265">
-      <c r="A1265" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1265" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1265" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D1265" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/risk-operations-program-manager-at-stripe-4440883915?refId=%2Bdyox2Xxoya8H1os%2BJqr%2Bg%3D%3D&amp;trackingId=%2BhAShAezY95tBh3RyiIvfQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1266">
-      <c r="A1266" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1266" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1266" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="D1266" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/jobs/view/business-analyst-operations-at-adyen-4449181007?refId=42LfBSOufBhvYUAOL7Y9gw%3D%3D&amp;trackingId=4HSiuDEF191PdMumcLWYLw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1267">
-      <c r="A1267" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1267" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1267" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1267" t="inlineStr">
-        <is>
-          <t>https://cd.linkedin.com/jobs/view/business-development-manager-at-visa-4449665928?refId=aK3Yk7SO5lStab1R44KsRw%3D%3D&amp;trackingId=Fqdc7yjswJv4naJG5KN7kA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1268">
-      <c r="A1268" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1268" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1268" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1268" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="1269">
-      <c r="A1269" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1269" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1269" t="inlineStr">
-        <is>
-          <t>Payoneer</t>
-        </is>
-      </c>
-      <c r="D1269" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/senior-business-development-manager-at-payoneer-4440576894?refId=AEl5xhJHRfxwAuXkc02n7A%3D%3D&amp;trackingId=kjpFnNTkVmgD%2BgUw5rkCBA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1270">
-      <c r="A1270" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1270" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1270" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1270" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/741af157-0000-4097-b13c-1e4677a7db49/director-channel-partnerships-sme-growth-americas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1271">
-      <c r="A1271" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1271" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1271" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1271" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1272">
-      <c r="A1272" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1272" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1272" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1272" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/f22a8795-d79c-4b80-8e92-92f724d3d23f/manager-growth-strategy-operations/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1273">
-      <c r="A1273" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1273" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1273" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1273" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/f6c340cc-7c3f-4706-96c6-07e78dcb1118/scaled-customer-success-manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1274">
-      <c r="A1274" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1274" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1274" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1274" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1275">
-      <c r="A1275" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1275" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1275" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1275" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1276">
-      <c r="A1276" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1276" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1276" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="D1276" t="inlineStr">
-        <is>
-          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1277">
-      <c r="A1277" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1277" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1277" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1277" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
-        </is>
-      </c>
-    </row>
-    <row r="1278">
-      <c r="A1278" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1278" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1278" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1278" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="1279">
-      <c r="A1279" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1279" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1279" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1279" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="1280">
-      <c r="A1280" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1280" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1280" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1280" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/money-transfer-operators</t>
-        </is>
-      </c>
-    </row>
-    <row r="1281">
-      <c r="A1281" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1281" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1281" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1281" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/marketplaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="1282">
-      <c r="A1282" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1282" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1282" t="inlineStr">
-        <is>
-          <t>Nium</t>
-        </is>
-      </c>
-      <c r="D1282" t="inlineStr">
-        <is>
-          <t>https://www.nium.com/solutions/airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="1283">
-      <c r="A1283" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1283" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1283" t="inlineStr">
-        <is>
-          <t>Checkout.com</t>
-        </is>
-      </c>
-      <c r="D1283" t="inlineStr">
-        <is>
-          <t>https://www.checkout.com/products/payment-links</t>
-        </is>
-      </c>
-    </row>
-    <row r="1284">
-      <c r="A1284" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1284" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1284" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1284" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/payment-solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="1285">
-      <c r="A1285" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1285" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1285" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1285" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/online-retail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1286">
-      <c r="A1286" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1286" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1286" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1286" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
-        </is>
-      </c>
-    </row>
-    <row r="1287">
-      <c r="A1287" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1287" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1287" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1287" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
-        </is>
-      </c>
-    </row>
-    <row r="1288">
-      <c r="A1288" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1288" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1288" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1288" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
-        </is>
-      </c>
-    </row>
-    <row r="1289">
-      <c r="A1289" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1289" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1289" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1289" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1290">
-      <c r="A1290" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1290" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1290" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1290" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1291">
-      <c r="A1291" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1291" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1291" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1291" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1292">
-      <c r="A1292" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1292" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1292" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1293">
-      <c r="A1293" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1293" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1293" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1293" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/issuing</t>
-        </is>
-      </c>
-    </row>
-    <row r="1294">
-      <c r="A1294" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1294" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1294" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/apm</t>
-        </is>
-      </c>
-    </row>
-    <row r="1295">
-      <c r="A1295" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1295" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1295" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1295" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/real-time-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1296">
-      <c r="A1296" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1296" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1296" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1296" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/bank-transfers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1297">
-      <c r="A1297" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1297" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1297" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1297" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1298">
-      <c r="A1298" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1298" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1298" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1298" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
-        </is>
-      </c>
-    </row>
-    <row r="1299">
-      <c r="A1299" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1299" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1299" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1299" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="1300">
-      <c r="A1300" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1300" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1300" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1300" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/currency-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1301">
-      <c r="A1301" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1301" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1301" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1301" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="1302">
-      <c r="A1302" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1302" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1302" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1302" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
-        </is>
-      </c>
-    </row>
-    <row r="1303">
-      <c r="A1303" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1303" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1303" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1303" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="1304">
-      <c r="A1304" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1304" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1304" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1304" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/hospitality</t>
-        </is>
-      </c>
-    </row>
-    <row r="1305">
-      <c r="A1305" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1305" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1305" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1305" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/automotive</t>
-        </is>
-      </c>
-    </row>
-    <row r="1306">
-      <c r="A1306" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1306" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1306" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1306" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/grocery</t>
-        </is>
-      </c>
-    </row>
-    <row r="1307">
-      <c r="A1307" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1307" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1307" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1307" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1308">
-      <c r="A1308" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1308" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1308" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1308" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
-        </is>
-      </c>
-    </row>
-    <row r="1309">
-      <c r="A1309" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1309" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1309" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1309" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/government</t>
-        </is>
-      </c>
-    </row>
-    <row r="1310">
-      <c r="A1310" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1310" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1310" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1310" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/business-to-business</t>
-        </is>
-      </c>
-    </row>
-    <row r="1311">
-      <c r="A1311" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1311" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1311" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1311" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/financial-services</t>
-        </is>
-      </c>
-    </row>
-    <row r="1312">
-      <c r="A1312" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1312" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1312" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1312" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/online-gaming</t>
-        </is>
-      </c>
-    </row>
-    <row r="1313">
-      <c r="A1313" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1313" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1313" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1313" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="1314">
-      <c r="A1314" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1314" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1314" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1314" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1315">
-      <c r="A1315" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1315" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1315" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1315" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="1316">
-      <c r="A1316" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1316" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1316" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1316" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="1317">
-      <c r="A1317" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1317" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1317" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1317" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="1318">
-      <c r="A1318" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1318" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1318" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1318" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="1319">
-      <c r="A1319" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1319" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1319" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1319" t="inlineStr">
-        <is>
-          <t>https://www.nuvei.com/posts/inside-nuveis-customer-advisory-board-7-things-the-smartest-merchants-think-about-payments-in-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1320">
-      <c r="A1320" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1320" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1320" t="inlineStr">
-        <is>
-          <t>Nuvei</t>
-        </is>
-      </c>
-      <c r="D1320" t="inlineStr">
-        <is>
-          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=KsHzcOBE4j1My%2F3PM9j3fA%3D%3D&amp;trackingId=JGTl8XCdMYF0b5L2DLVQlg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1321">
-      <c r="A1321" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1321" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1321" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1321" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1322">
-      <c r="A1322" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1322" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1322" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1322" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1323">
-      <c r="A1323" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1323" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1323" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1323" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1324">
-      <c r="A1324" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1324" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1324" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1324" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1325">
-      <c r="A1325" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1325" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1325" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1325" t="inlineStr">
-        <is>
-          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
-        </is>
-      </c>
-    </row>
-    <row r="1326">
-      <c r="A1326" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1326" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1326" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1326" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=9zmm6bwjwW%2BL6NDsuWRkAg%3D%3D&amp;trackingId=7U7Ci9nGDECNIL%2Bjbj7XVg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1327">
-      <c r="A1327" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1327" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1327" t="inlineStr">
-        <is>
-          <t>Fireblocks</t>
-        </is>
-      </c>
-      <c r="D1327" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1328">
-      <c r="A1328" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1328" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1328" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="D1328" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="1329">
-      <c r="A1329" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1329" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1329" t="inlineStr">
-        <is>
-          <t>BVNK</t>
-        </is>
-      </c>
-      <c r="D1329" t="inlineStr">
-        <is>
-          <t>https://www.bvnk.com/self-managed-payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="1330">
-      <c r="A1330" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1330" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1330" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1330" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1331" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1331" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1331" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1332">
-      <c r="A1332" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1332" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1332" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1332" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1333">
-      <c r="A1333" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1333" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1333" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1333" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1334">
-      <c r="A1334" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1334" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1334" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1334" t="inlineStr">
-        <is>
-          <t>https://bitpay.com/careers/directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="1335">
-      <c r="A1335" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1335" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1335" t="inlineStr">
-        <is>
-          <t>Triple-A</t>
-        </is>
-      </c>
-      <c r="D1335" t="inlineStr">
-        <is>
-          <t>https://triple-a.io/case-studies</t>
-        </is>
-      </c>
-    </row>
-    <row r="1336">
-      <c r="A1336" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1336" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1336" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1336" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=k3afJP%2BL8XgG4b%2BfdDzF%2BQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1337">
-      <c r="A1337" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1337" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1337" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1337" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/jobs/view/product-manager-payments-at-straitsx-4447696660?refId=Lf4xu6vi8d924V4b3CiecA%3D%3D&amp;trackingId=7ISJGq2BR4QhXl0Tp7D7hg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1338">
-      <c r="A1338" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1338" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1338" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1338" t="inlineStr">
-        <is>
-          <t>https://unlimit.com/ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="1339">
-      <c r="A1339" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1339" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1339" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1339" t="inlineStr">
-        <is>
-          <t>https://unlimit.com/ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="1340">
-      <c r="A1340" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1340" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1340" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1340" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
-        </is>
-      </c>
-    </row>
-    <row r="1341">
-      <c r="A1341" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1341" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1341" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1341" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
-        </is>
-      </c>
-    </row>
-    <row r="1342">
-      <c r="A1342" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1342" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1342" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1342" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
-        </is>
-      </c>
-    </row>
-    <row r="1343">
-      <c r="A1343" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1343" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1343" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1343" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
-        </is>
-      </c>
-    </row>
-    <row r="1344">
-      <c r="A1344" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1344" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D1344" t="inlineStr">
-        <is>
-          <t>https://ie.linkedin.com/jobs/view/manager-field-security-specialists-cyber-solutions-engineering-at-openai-4449308650?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=W5gADlCRGJ5aaYSJTSROIQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1345">
-      <c r="A1345" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1345" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C1345" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D1345" t="inlineStr">
-        <is>
-          <t>https://in.linkedin.com/jobs/view/customer-success-manager-ads-solutions-mumbai-at-openai-4449317487?refId=r6ltbAno6efYUyXR8nspLA%3D%3D&amp;trackingId=iHg5gALrXxmg4%2FX%2FN4rIkA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="1346">
-      <c r="A1346" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1346" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1346" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1346" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1347">
-      <c r="A1347" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1347" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1347" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1347" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1348">
-      <c r="A1348" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1348" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1348" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1348" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1349">
-      <c r="A1349" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1349" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1349" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1349" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/posts/tags/payment-operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="1350">
-      <c r="A1350" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1350" t="inlineStr">
-        <is>
-          <t>UPDATED</t>
-        </is>
-      </c>
-      <c r="C1350" t="inlineStr">
-        <is>
-          <t>Wise</t>
-        </is>
-      </c>
-      <c r="D1350" t="inlineStr">
-        <is>
-          <t>https://wise.jobs/wise-platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="1351">
-      <c r="A1351" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1351" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1351" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D1351" t="inlineStr">
-        <is>
-          <t>https://jobs.visa.com/</t>
-        </is>
-      </c>
-      <c r="E1351" t="inlineStr">
-        <is>
-          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
-        </is>
-      </c>
-    </row>
-    <row r="1352">
-      <c r="A1352" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1352" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr">
-        <is>
-          <t>Checkout.com</t>
-        </is>
-      </c>
-      <c r="D1352" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
-        </is>
-      </c>
-      <c r="E1352" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1353">
-      <c r="A1353" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1353" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1353" t="inlineStr">
-        <is>
-          <t>Thunes</t>
-        </is>
-      </c>
-      <c r="D1353" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/thunes/jobs/</t>
-        </is>
-      </c>
-      <c r="E1353" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1354">
-      <c r="A1354" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1354" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1354" t="inlineStr">
-        <is>
-          <t>Rapyd</t>
-        </is>
-      </c>
-      <c r="D1354" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
-        </is>
-      </c>
-      <c r="E1354" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1355">
-      <c r="A1355" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1355" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1355" t="inlineStr">
-        <is>
-          <t>Circle</t>
-        </is>
-      </c>
-      <c r="D1355" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/circle/jobs/</t>
-        </is>
-      </c>
-      <c r="E1355" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1356">
-      <c r="A1356" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1356" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1356" t="inlineStr">
-        <is>
-          <t>Ripple</t>
-        </is>
-      </c>
-      <c r="D1356" t="inlineStr">
-        <is>
-          <t>https://ripple.com/careers/</t>
-        </is>
-      </c>
-      <c r="E1356" t="inlineStr">
-        <is>
-          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
-        </is>
-      </c>
-    </row>
-    <row r="1357">
-      <c r="A1357" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1357" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1357" t="inlineStr">
-        <is>
-          <t>BitPay</t>
-        </is>
-      </c>
-      <c r="D1357" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
-        </is>
-      </c>
-      <c r="E1357" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1358">
-      <c r="A1358" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1358" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1358" t="inlineStr">
-        <is>
-          <t>StraitsX</t>
-        </is>
-      </c>
-      <c r="D1358" t="inlineStr">
-        <is>
-          <t>https://www.straitsx.com/careers</t>
-        </is>
-      </c>
-      <c r="E1358" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1359">
-      <c r="A1359" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1359" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1359" t="inlineStr">
-        <is>
-          <t>OSL</t>
-        </is>
-      </c>
-      <c r="D1359" t="inlineStr">
-        <is>
-          <t>https://osl.com/careers/</t>
-        </is>
-      </c>
-      <c r="E1359" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1360">
-      <c r="A1360" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1360" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1360" t="inlineStr">
-        <is>
-          <t>Unlimit</t>
-        </is>
-      </c>
-      <c r="D1360" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
-        </is>
-      </c>
-      <c r="E1360" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1361">
-      <c r="A1361" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1361" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1361" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="D1361" t="inlineStr">
-        <is>
-          <t>https://www.okx.com/careers</t>
-        </is>
-      </c>
-      <c r="E1361" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1362">
-      <c r="A1362" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1362" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1362" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="D1362" t="inlineStr">
-        <is>
-          <t>https://www.gate.io/careers</t>
-        </is>
-      </c>
-      <c r="E1362" t="inlineStr">
-        <is>
-          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1363">
-      <c r="A1363" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1363" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1363" t="inlineStr">
-        <is>
-          <t>Reap</t>
-        </is>
-      </c>
-      <c r="D1363" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
-        </is>
-      </c>
-      <c r="E1363" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1364">
-      <c r="A1364" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1364" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1364" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="D1364" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-      <c r="E1364" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1365">
-      <c r="A1365" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1365" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1365" t="inlineStr">
-        <is>
-          <t>Skyfire</t>
-        </is>
-      </c>
-      <c r="D1365" t="inlineStr">
-        <is>
-          <t>https://www.skyfire.xyz/careers</t>
-        </is>
-      </c>
-      <c r="E1365" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
-        </is>
-      </c>
-    </row>
-    <row r="1366">
-      <c r="A1366" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1366" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1366" t="inlineStr">
-        <is>
-          <t>Skyfire</t>
-        </is>
-      </c>
-      <c r="D1366" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-      <c r="E1366" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1367">
-      <c r="A1367" t="inlineStr">
-        <is>
-          <t>2026-08-06 17:23:41</t>
-        </is>
-      </c>
-      <c r="B1367" t="inlineStr">
-        <is>
-          <t>SCAN_FAILED</t>
-        </is>
-      </c>
-      <c r="C1367" t="inlineStr">
-        <is>
-          <t>Nevermined</t>
-        </is>
-      </c>
-      <c r="D1367" t="inlineStr">
-        <is>
-          <t>https://nevermined.io/careers</t>
-        </is>
-      </c>
-      <c r="E1367" t="inlineStr">
-        <is>
-          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
         </is>
       </c>
     </row>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -4541,7 +4541,17 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>To Review</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>A1 TEST</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8142,6 @@
       <c r="F10" t="n">
         <v>28</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Partial</t>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Chongqing</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Ningbo</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 09:52:48</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -7210,6 +7210,461 @@
         </is>
       </c>
       <c r="J193" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Enterprise Account Manager</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>25</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/enterprise-account-manager-at-adyen-4449755101?refId=nB3DAT0565mHtbgaf3UuCg%3D%3D&amp;trackingId=O4ZEk1rw4z%2FwpkgD0cnwdA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Manager, Corporate Solutions - Program Management Office - Product Governance and Launch</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>35</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/manager-corporate-solutions-program-management-office-product-governance-and-launch-at-mastercard-4448479543?refId=uv8gDeZ6%2BXDK2yrQ2EuFTQ%3D%3D&amp;trackingId=wJths%2F7CCNVbhMUbQ7NYnQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Product Manager - B2B Payments</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>25</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/product-manager-b2b-payments-at-mastercard-4448470916?refId=uv8gDeZ6%2BXDK2yrQ2EuFTQ%3D%3D&amp;trackingId=3kUn1pXosu4C6s2YHJ8ojw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Credit Risk Manager - Strategic Partnerships</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>45</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/credit-risk-manager-strategic-partnerships-at-paypal-4422420882?refId=JLj52uZuuTvsnfaiCoeYwA%3D%3D&amp;trackingId=dwuzJTYC0dp%2FQGh8jOsHkw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Business Operations &amp; Analytics, Working Capital</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>25</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=%2Bt73Ta63UTHkAt4Mgcp%2Fdw%3D%3D&amp;trackingId=4nLgvA3DewElIvCBVfruYQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Manager, Growth Strategy &amp; Operations (Singapore-based)Operations ManagementAmericas, San Francisco</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>25</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/719b124a-74a6-4ae5-884f-2bca6b81963c/manager-growth-strategy-operations-singapore-based/</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Account Executive, SME &amp; Growth</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>25</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448426828?refId=u7AzqowVMr33KFSWCtnMUw%3D%3D&amp;trackingId=9WXasY80L0gty4QccwAmQg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Account Executive, SME &amp; Growth</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>25</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448412919?refId=u7AzqowVMr33KFSWCtnMUw%3D%3D&amp;trackingId=Skk0YQY%2FzVwrkqppx0X%2B%2Bg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Enterprise Account Executive, B2B</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>40</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=OF3BOuQmEyf%2B%2B6gy1xARQw%3D%3D&amp;trackingId=Huf9jirmd%2FcnOTcVEpg7Gg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>40</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=OF3BOuQmEyf%2B%2B6gy1xARQw%3D%3D&amp;trackingId=Kqa2s%2F5g9evaGQplRVZ9og%3D%3D</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>VP, Customer Success</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>35</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=PxRzV%2FjKsKfM964e15PLRg%3D%3D&amp;trackingId=EnWO2taOYWeX%2B5pZ%2B7KB6A%3D%3D</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Global Head of Business Operations - Wise Platform</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>25</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/global-head-of-business-operations-wise-platform-in-london-jid-3910</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Global Head of Business Operations - Wise Platform</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>25</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/global-head-of-business-operations-wise-platform-in-london-jid-3910</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -7860,7 +8315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8143,6 +8598,34 @@
         <v>28</v>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>76</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8159,7 +8642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1026"/>
+  <dimension ref="A1:E1146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31999,6 +32482,2801 @@
         </is>
       </c>
     </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/enterprise-account-manager-at-adyen-4449755101?refId=nB3DAT0565mHtbgaf3UuCg%3D%3D&amp;trackingId=O4ZEk1rw4z%2FwpkgD0cnwdA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/manager-corporate-solutions-program-management-office-product-governance-and-launch-at-mastercard-4448479543?refId=uv8gDeZ6%2BXDK2yrQ2EuFTQ%3D%3D&amp;trackingId=wJths%2F7CCNVbhMUbQ7NYnQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/product-manager-b2b-payments-at-mastercard-4448470916?refId=uv8gDeZ6%2BXDK2yrQ2EuFTQ%3D%3D&amp;trackingId=3kUn1pXosu4C6s2YHJ8ojw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/credit-risk-manager-strategic-partnerships-at-paypal-4422420882?refId=JLj52uZuuTvsnfaiCoeYwA%3D%3D&amp;trackingId=dwuzJTYC0dp%2FQGh8jOsHkw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=%2Bt73Ta63UTHkAt4Mgcp%2Fdw%3D%3D&amp;trackingId=4nLgvA3DewElIvCBVfruYQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/719b124a-74a6-4ae5-884f-2bca6b81963c/manager-growth-strategy-operations-singapore-based/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448426828?refId=u7AzqowVMr33KFSWCtnMUw%3D%3D&amp;trackingId=9WXasY80L0gty4QccwAmQg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448412919?refId=u7AzqowVMr33KFSWCtnMUw%3D%3D&amp;trackingId=Skk0YQY%2FzVwrkqppx0X%2B%2Bg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=OF3BOuQmEyf%2B%2B6gy1xARQw%3D%3D&amp;trackingId=Huf9jirmd%2FcnOTcVEpg7Gg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=OF3BOuQmEyf%2B%2B6gy1xARQw%3D%3D&amp;trackingId=Kqa2s%2F5g9evaGQplRVZ9og%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=PxRzV%2FjKsKfM964e15PLRg%3D%3D&amp;trackingId=EnWO2taOYWeX%2B5pZ%2B7KB6A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/global-head-of-business-operations-wise-platform-in-london-jid-3910</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/global-head-of-business-operations-wise-platform-in-london-jid-3910</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>504 Server Error: Gateway Timeout for url: https://www.fireblocks.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://fr.linkedin.com/company/okx</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:52:48</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -2896,7 +2896,13 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>To Review</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8630,6 @@
       <c r="F11" t="n">
         <v>31</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Partial</t>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -2899,7 +2899,6 @@
           <t>To Review</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>test</t>
@@ -5817,7 +5816,17 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>test1</t>
         </is>
       </c>
     </row>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -6176,7 +6176,17 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>To Review</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>final sync test</t>
         </is>
       </c>
     </row>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesAPAC, Ningbo</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•ShanghaiAPAC,ShanghaiShanghai</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; GrowthSalesAPAC, Shanghai</t>
+          <t>Account Executive, Outbound, SME &amp; GrowthSalesSales•Xi'anAPAC,Xi'anXi'an</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-05 17:35:46</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•YiwuAPAC,YiwuYiwu</t>
+          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -7686,10 +7686,535 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-08-07 09:52:48</t>
+          <t>2026-08-07 13:43:30</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Enterprise Account Manager</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>25</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/enterprise-account-manager-at-adyen-4449755101?refId=Rz9S8fw3rQ9Rai0kIpG2Pw%3D%3D&amp;trackingId=pGt%2BnGXn2ESRTruFfeCAxA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Manager, Corporate Solutions - Program Management Office - Product Governance and Launch</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>35</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/manager-corporate-solutions-program-management-office-product-governance-and-launch-at-mastercard-4448479543?refId=cSMXeMlftgB6T0bFO%2BsILA%3D%3D&amp;trackingId=uVq3fDemhH8GmMUo3dF1bw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Product Manager - B2B Payments</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>25</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/product-manager-b2b-payments-at-mastercard-4448470916?refId=cSMXeMlftgB6T0bFO%2BsILA%3D%3D&amp;trackingId=X4M73fRbmJAFgHveSohRUw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Credit Risk Manager - Strategic Partnerships</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>45</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/credit-risk-manager-strategic-partnerships-at-paypal-4422420882?refId=8EMlsPrN4SnS0nFcK7BmIg%3D%3D&amp;trackingId=V9hIKGopxoLPNpRzUBFQaA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Business Operations &amp; Analytics, Working Capital</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>25</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=aPsCT1WS5KzZfbgL9Axviw%3D%3D&amp;trackingId=wNPtoqfoMQNSnHmkH6vcpg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Account Executive (Education Segment)SalesSales•SingaporeAPAC,SingaporeSingapore</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>25</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d30babad-fce1-49f7-ae97-1248444f357b/account-executive-education-segment/</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Manager, Global Growth, LifecycleOperations ManagementOperations Management•San FranciscoAmericas,San FranciscoSan Francisco</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>25</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/971599e5-e353-4f88-9a7c-2114251b2d2e/manager-global-growth-lifecycle/</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Channel Partnerships Manager, DACHSalesBerlin</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>50</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/e152b49c-39ad-4d00-8d54-98d1c3bd78fe/channel-partnerships-manager-dach/</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Account Executive, SME &amp; Growth</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>25</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448412919?refId=XEUOUtRoX4XLyrVx2MtSHA%3D%3D&amp;trackingId=jyHr5nH12jK7PhUrdekW7w%3D%3D</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Account Executive, SME &amp; Growth</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>25</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448426828?refId=XEUOUtRoX4XLyrVx2MtSHA%3D%3D&amp;trackingId=qhn96RO%2Bbc0an%2BSMGoAQ5Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Enterprise Account Executive, B2B</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>40</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=6m5tIgvLTqfNP2qxuX82pg%3D%3D&amp;trackingId=1NYiovBLqQC4Jh%2FdE3ArQg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Business Development Manager- Mexico</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>40</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=6m5tIgvLTqfNP2qxuX82pg%3D%3D&amp;trackingId=KHLA%2FGXG44%2Bo3WEOHJrm8Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>VP, Customer Success</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>35</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=NXbNsa8jygJt14UsM7Oi7Q%3D%3D&amp;trackingId=N6fVxxgTrwd6kl3rtB5S6Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Commercial Sales Associate</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=PA1ponXnEwUdsFFZ1Bn9cQ%3D%3D&amp;trackingId=O3Iq9y%2BjL8xzCDO4Y247ng%3D%3D</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>JOB-20260807-0220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Enterprise Product Growth Manager</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-product-growth-manager-at-perplexity-4440647361?refId=vQ5EwLYKX9e4nSQ7itnCgA%3D%3D&amp;trackingId=jOnJBDueWhAzBPJ%2Fe416wg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -8340,7 +8865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8650,6 +9175,34 @@
         <v>31</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8666,7 +9219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1146"/>
+  <dimension ref="A1:E1260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35301,6 +35854,2594 @@
         </is>
       </c>
     </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/jobs/view/enterprise-account-manager-at-adyen-4449755101?refId=Rz9S8fw3rQ9Rai0kIpG2Pw%3D%3D&amp;trackingId=pGt%2BnGXn2ESRTruFfeCAxA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/manager-corporate-solutions-program-management-office-product-governance-and-launch-at-mastercard-4448479543?refId=cSMXeMlftgB6T0bFO%2BsILA%3D%3D&amp;trackingId=uVq3fDemhH8GmMUo3dF1bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/product-manager-b2b-payments-at-mastercard-4448470916?refId=cSMXeMlftgB6T0bFO%2BsILA%3D%3D&amp;trackingId=X4M73fRbmJAFgHveSohRUw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/credit-risk-manager-strategic-partnerships-at-paypal-4422420882?refId=8EMlsPrN4SnS0nFcK7BmIg%3D%3D&amp;trackingId=V9hIKGopxoLPNpRzUBFQaA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=aPsCT1WS5KzZfbgL9Axviw%3D%3D&amp;trackingId=wNPtoqfoMQNSnHmkH6vcpg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/9a87615c-17d7-4b94-b2ad-fb1e72c74e74/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/d30babad-fce1-49f7-ae97-1248444f357b/account-executive-education-segment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/971599e5-e353-4f88-9a7c-2114251b2d2e/manager-global-growth-lifecycle/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/e152b49c-39ad-4d00-8d54-98d1c3bd78fe/channel-partnerships-manager-dach/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448412919?refId=XEUOUtRoX4XLyrVx2MtSHA%3D%3D&amp;trackingId=jyHr5nH12jK7PhUrdekW7w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/account-executive-sme-growth-at-airwallex-4448426828?refId=XEUOUtRoX4XLyrVx2MtSHA%3D%3D&amp;trackingId=qhn96RO%2Bbc0an%2BSMGoAQ5Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=6m5tIgvLTqfNP2qxuX82pg%3D%3D&amp;trackingId=1NYiovBLqQC4Jh%2FdE3ArQg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/jobs/view/business-development-manager-mexico-at-nuvei-4449184879?refId=6m5tIgvLTqfNP2qxuX82pg%3D%3D&amp;trackingId=KHLA%2FGXG44%2Bo3WEOHJrm8Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/vp-customer-success-at-fireblocks-4449687250?refId=NXbNsa8jygJt14UsM7Oi7Q%3D%3D&amp;trackingId=N6fVxxgTrwd6kl3rtB5S6Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/commercial-sales-associate-at-straitsx-4448019371?refId=PA1ponXnEwUdsFFZ1Bn9cQ%3D%3D&amp;trackingId=O3Iq9y%2BjL8xzCDO4Y247ng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-product-growth-manager-at-perplexity-4440647361?refId=vQ5EwLYKX9e4nSQ7itnCgA%3D%3D&amp;trackingId=jOnJBDueWhAzBPJ%2Fe416wg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/global-head-of-business-operations-wise-platform-in-london-jid-3910</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/global-head-of-business-operations-wise-platform-in-london-jid-3910</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:43:30</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -9201,7 +9201,6 @@
       <c r="F12" t="n">
         <v>16</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Partial</t>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -4546,7 +4546,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>To Review</t>
+          <t>Applied</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -2896,9 +2896,10 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>To Review</t>
-        </is>
-      </c>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>test</t>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -2899,7 +2899,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>test</t>
@@ -6177,7 +6176,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>To Review</t>
+          <t>Watching</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 08:01:02</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -8215,6 +8215,426 @@
         </is>
       </c>
       <c r="J221" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>35</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424970219?refId=PV70Xe6Vpmi4lINss9hlFg%3D%3D&amp;trackingId=NGZReHk0ISObyTh6cT%2FScw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>35</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424958275?refId=PV70Xe6Vpmi4lINss9hlFg%3D%3D&amp;trackingId=PbDryi%2BPd1fyhFTnUrBw4A%3D%3D</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Business Analyst, Sales &amp; Commercial Operations</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>50</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/business-analyst-sales-commercial-operations-at-visa-4450384645?refId=huOBNaudSZrak1Levv0z4A%3D%3D&amp;trackingId=lYvdyqqR9l9%2BG2u2KPgGkA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Business Development Representative, WFM</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>40</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/business-development-representative-wfm-at-payoneer-4450307361?refId=Sh3Em2a8v4Y7YsnLtbDChw%3D%3D&amp;trackingId=hRHIVPK9rVkugoDRVaB6KQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Business Operations &amp; Analytics, Working Capital</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>25</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=Sh3Em2a8v4Y7YsnLtbDChw%3D%3D&amp;trackingId=kMbA9iMwsiK1XGTW%2Bl6D1Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Senior Manager, Growth Strategy &amp; Operations (Singapore-based)Operations ManagementOperations Management•San FranciscoAmericas,San FranciscoSan Francisco</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>25</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/a25efb5d-bc29-4141-967e-c338a353c9a9/senior-manager-growth-strategy-operations-singapore-based/</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Senior Manager, Financial Partnerships APACFinancial and Strategic PartnershipsFinancial and Strategic Partnerships•SingaporeAPAC,SingaporeSingapore</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>45</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/00a7bbce-af16-4d4d-b36b-50034b5d9038/senior-manager-financial-partnerships-apac/</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Enterprise Account Executive, B2B</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>40</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=%2Fmy0E2j3LHoF1urBSHaY5Q%3D%3D&amp;trackingId=2cYbSoGgsgaxUXAXfflVpg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sales Director, Enterprise</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>25</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sales-director-enterprise-at-fireblocks-4441678999?refId=3xWRBCojVJ%2BgZxsNuTrehw%3D%3D&amp;trackingId=Gu4y0LIOtPx%2F%2BQqbOR%2Ff%2Bw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>35</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>35</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>35</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -8865,7 +9285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9202,6 +9622,34 @@
         <v>16</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>76</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>29</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9218,7 +9666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1260"/>
+  <dimension ref="A1:E1379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38441,6 +38889,2769 @@
         </is>
       </c>
     </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424970219?refId=PV70Xe6Vpmi4lINss9hlFg%3D%3D&amp;trackingId=NGZReHk0ISObyTh6cT%2FScw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424958275?refId=PV70Xe6Vpmi4lINss9hlFg%3D%3D&amp;trackingId=PbDryi%2BPd1fyhFTnUrBw4A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/business-analyst-sales-commercial-operations-at-visa-4450384645?refId=huOBNaudSZrak1Levv0z4A%3D%3D&amp;trackingId=lYvdyqqR9l9%2BG2u2KPgGkA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/business-development-representative-wfm-at-payoneer-4450307361?refId=Sh3Em2a8v4Y7YsnLtbDChw%3D%3D&amp;trackingId=hRHIVPK9rVkugoDRVaB6KQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=Sh3Em2a8v4Y7YsnLtbDChw%3D%3D&amp;trackingId=kMbA9iMwsiK1XGTW%2Bl6D1Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/a25efb5d-bc29-4141-967e-c338a353c9a9/senior-manager-growth-strategy-operations-singapore-based/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/00a7bbce-af16-4d4d-b36b-50034b5d9038/senior-manager-financial-partnerships-apac/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=%2Fmy0E2j3LHoF1urBSHaY5Q%3D%3D&amp;trackingId=2cYbSoGgsgaxUXAXfflVpg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sales-director-enterprise-at-fireblocks-4441678999?refId=3xWRBCojVJ%2BgZxsNuTrehw%3D%3D&amp;trackingId=Gu4y0LIOtPx%2F%2BQqbOR%2Ff%2Bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/payment-operations-regional-product-specialist-in-austin-jid-3555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:02</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:01:03</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L233"/>
+  <dimension ref="A1:L261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•ShanghaiAPAC,ShanghaiShanghai</t>
+          <t>Account Executive, B2B, SME &amp; GrowthSalesSales•ChongqingAPAC,ChongqingChongqing</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Online retailEcommerce payment solutions</t>
+          <t>Online retail|Nuveinuvei.com/use-cases/online-retailElevate your online store with Nuvei. Offer 700 payment methods and boost global sales. Start optimizing today.</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•ShenzhenAPAC,ShenzhenShenzhen</t>
+          <t>Account Executive, Outbound, SME &amp; Growth,SalesSales•QingdaoAPAC,QingdaoQingdao</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-07 13:43:30</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-06 08:52:31</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -8631,10 +8631,990 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 20:56:47</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>35</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424957337?refId=KymIg6oC4SgQrT%2BAwggPuA%3D%3D&amp;trackingId=JKTEUFuIC28efcb%2FG6oBug%3D%3D</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>35</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424970219?refId=KymIg6oC4SgQrT%2BAwggPuA%3D%3D&amp;trackingId=k3vAEK00s0Ev9d%2FL453IDg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>35</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424958275?refId=KymIg6oC4SgQrT%2BAwggPuA%3D%3D&amp;trackingId=giwH03bRV9ZLlc1ortDXPw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Enterprise Account Manager, Adyen for Platforms</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>25</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/enterprise-account-manager-adyen-for-platforms-at-adyen-4360814131?refId=z7DpB7BDFhuFalOtmxk%2BYQ%3D%3D&amp;trackingId=x%2BlTYNHy6fhHk1yGWkn6og%3D%3D</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Business Development Leader</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>40</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://vn.linkedin.com/jobs/view/business-development-leader-at-visa-4414536869?refId=081TIuS1y3PvNFqOFaQEhw%3D%3D&amp;trackingId=8D07TwRLBcmyQO4yXeA6Qw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sr Manager, Visa Commercial Solutions (Commercial Product – Fleet)</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>55</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/jobs/view/sr-manager-visa-commercial-solutions-commercial-product-%E2%80%93-fleet-at-visa-4406144416?refId=081TIuS1y3PvNFqOFaQEhw%3D%3D&amp;trackingId=NR%2Fe1%2B%2Bqew7TG0trMfWsKQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Director, Customer Success</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>35</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-customer-success-at-mastercard-4451038558?refId=ozIm3NS3UTlhf1W%2Ft2OEBA%3D%3D&amp;trackingId=%2BNRAVREuAUhgM9NMuZRCcA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Director, Commercial Integration &amp; Revenue Performance-Recorded Future Partnership</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>30</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-commercial-integration-revenue-performance-recorded-future-partnership-at-mastercard-4451033711?refId=ozIm3NS3UTlhf1W%2Ft2OEBA%3D%3D&amp;trackingId=RtgxyEdn2gm2vDv%2Bz7EwYQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Business Development Representative, WFM</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>40</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/business-development-representative-wfm-at-payoneer-4450307361?refId=aOlrJ%2BFg59IhQJ%2BhHCczMw%3D%3D&amp;trackingId=5k5lTUFtpYkYmBqR8RwGTQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Business Operations &amp; Analytics, Working Capital</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>25</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=aOlrJ%2BFg59IhQJ%2BhHCczMw%3D%3D&amp;trackingId=tZibRpErkF%2BW1n1guwjxpg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Account Executive/Senior Account Executive, Enterprise (Travel Vertical)SalesAPAC, Singapore</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>45</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b2a5c56c-2691-4c4e-b522-5f635ac7d4d5/account-executive-senior-account-executive-enterprise-travel-vertical/</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Senior Manager, Growth Strategy &amp; Operations (Singapore-based)</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>25</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-growth-strategy-operations-singapore-based-at-airwallex-4351930654?refId=ETxZu68ZG65yU9AtXRKdTg%3D%3D&amp;trackingId=EsUt%2Bae2UOQn5322Ci4lXA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Travel Platform DocsOptimize payments to online travel agencies, airlines and hotels</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>30</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Travel Platform DocsOptimize payments to online travel agencies, airlines and hotels</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>30</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>How Europe pays: payment preferences across five markets (2026 research)|Nuveinuvei.com/posts/how-europe-pays-payment-preferences-across-five-markets-2026-researchNuvei’s How Europe Pays research with Sapio surveyed 5,000 consumers across the UK, Germany, Italy, Poland, and Benelux in July 2026. The study finds 27% of Europeans abandon purchases when their preferred payment method is missing, 26% expect websites to offer their way to pay, 67% want to approve every purchase themselves, and only 19% are comfortable letting an AI assistant complete a transaction—showing that local payment methods and trusted checkout experiences now decide who wins the sale.</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>30</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/how-europe-pays-payment-preferences-across-five-markets-2026-research</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>How America Pays: What 1,000 US shoppers told Nuvei|Nuveinuvei.com/posts/how-america-pays-what-1-000-us-shoppers-told-nuveiNuvei’s How America Pays survey of 1,000 US consumers shows payment choice is now a revenue and brand variable. Sixty percent strongly prefer to personally review and approve every purchase, 21% would abandon a transaction if their preferred method is missing (with 37% leaning that way), and 45% would rather wait and see how others use AI for purchasing before trying it themselves. Learn how fixed payment habits, demand for methods beyond cards, and caution about AI-driven purchasing should shape your checkout and payments strategy.</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>40</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/how-america-pays-what-1-000-us-shoppers-told-nuvei</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Agentic commerce: What it is and how payments have to change|Nuveinuvei.com/posts/agentic-commerce-what-it-is-and-how-payments-have-to-changeAgentic commerce is a model where AI agents act as the buyer, finding products and completing payments inside the agent instead of a traditional checkout. McKinsey projects $1T in agentic transaction volume by 2030 and $3–5T by 2035. Explore why existing payment rails struggle with agent-initiated purchases, what consumers need to trust AI with spend, and how Nuvei Agentic—via its Protocol Compatibility Layer and Know Your Agent—creates a single execution layer any AI agent can call to pay.</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>35</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/agentic-commerce-what-it-is-and-how-payments-have-to-change</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager- Brazil</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>40</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/jobs/view/senior-business-development-manager-brazil-at-nuvei-4441367054?refId=WcXTRtyALhxud2A7LehG1w%3D%3D&amp;trackingId=BlscybedpAe9SVy2JE4QXw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Enterprise Account Executive, B2B</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>40</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=WcXTRtyALhxud2A7LehG1w%3D%3D&amp;trackingId=0JwlLLBAuV7dCsBZo3BnLQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>󰄾Payment FirmsNear-instant, low-cost, global payment rails for modern providers</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>25</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/developer-platform/paymentfirms</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Sales Director, Enterprise</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>25</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sales-director-enterprise-at-fireblocks-4441678999?refId=PUikLmtgyEMIL7fQqVs7QA%3D%3D&amp;trackingId=f6AbQ9gByYEbF4%2FiQX9jUQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Country &amp; Payment CoverageExplore all available payment methods in countries worldwide.</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>25</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Country &amp; Payment CoverageExplore all available payment methods in countries worldwide.</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>25</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Payment rails</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>25</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Payment rails</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>25</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Payment rails</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>25</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Agentic PaymentsEnabling AI agents to transact on behalf of individuals and businesses.</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>35</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Agentic PaymentsEnabling AI agents to transact on behalf of individuals and businesses.</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>35</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -9285,7 +10265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9648,8 +10628,35 @@
       <c r="F13" t="n">
         <v>29</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>76</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9666,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1379"/>
+  <dimension ref="A1:E1525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41652,6 +42659,3373 @@
         </is>
       </c>
     </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7993151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-grower-japanese-fluency/8042978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-commercial-hunter-japanese-fluency/7789539</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-cross-border-china/7893199</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-grower/7997555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424957337?refId=KymIg6oC4SgQrT%2BAwggPuA%3D%3D&amp;trackingId=JKTEUFuIC28efcb%2FG6oBug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424970219?refId=KymIg6oC4SgQrT%2BAwggPuA%3D%3D&amp;trackingId=k3vAEK00s0Ev9d%2FL453IDg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424958275?refId=KymIg6oC4SgQrT%2BAwggPuA%3D%3D&amp;trackingId=giwH03bRV9ZLlc1ortDXPw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/enterprise-account-manager-adyen-for-platforms-at-adyen-4360814131?refId=z7DpB7BDFhuFalOtmxk%2BYQ%3D%3D&amp;trackingId=x%2BlTYNHy6fhHk1yGWkn6og%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>https://vn.linkedin.com/jobs/view/business-development-leader-at-visa-4414536869?refId=081TIuS1y3PvNFqOFaQEhw%3D%3D&amp;trackingId=8D07TwRLBcmyQO4yXeA6Qw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/jobs/view/sr-manager-visa-commercial-solutions-commercial-product-%E2%80%93-fleet-at-visa-4406144416?refId=081TIuS1y3PvNFqOFaQEhw%3D%3D&amp;trackingId=NR%2Fe1%2B%2Bqew7TG0trMfWsKQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/visa-commercial-solutions-vcs/?trk=affiliated-pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-customer-success-at-mastercard-4451038558?refId=ozIm3NS3UTlhf1W%2Ft2OEBA%3D%3D&amp;trackingId=%2BNRAVREuAUhgM9NMuZRCcA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-commercial-integration-revenue-performance-recorded-future-partnership-at-mastercard-4451033711?refId=ozIm3NS3UTlhf1W%2Ft2OEBA%3D%3D&amp;trackingId=RtgxyEdn2gm2vDv%2Bz7EwYQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/business-development-representative-wfm-at-payoneer-4450307361?refId=aOlrJ%2BFg59IhQJ%2BhHCczMw%3D%3D&amp;trackingId=5k5lTUFtpYkYmBqR8RwGTQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/jobs/view/sr-manager-business-operations-analytics-working-capital-at-payoneer-4450292204?refId=aOlrJ%2BFg59IhQJ%2BhHCczMw%3D%3D&amp;trackingId=tZibRpErkF%2BW1n1guwjxpg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/6df32f20-e872-42ce-81d1-1abd35d4a9b3/account-executive-outbound-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/1e224584-b55c-4755-bdad-dfd1ca995764/account-executive-b2b-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b2a5c56c-2691-4c4e-b522-5f635ac7d4d5/account-executive-senior-account-executive-enterprise-travel-vertical/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-solutions-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-growth-strategy-operations-singapore-based-at-airwallex-4351930654?refId=ETxZu68ZG65yU9AtXRKdTg%3D%3D&amp;trackingId=EsUt%2Bae2UOQn5322Ci4lXA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/money-transfer-operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>https://www.checkout.com/products/payment-links</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/canada-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/uk-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/eu-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/us-bank-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/bank-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/reconciliation-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/currency-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/fraud-risk-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/authorization-optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/how-europe-pays-payment-preferences-across-five-markets-2026-research</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/how-america-pays-what-1-000-us-shoppers-told-nuvei</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/agentic-commerce-what-it-is-and-how-payments-have-to-change</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/jobs/view/senior-business-development-manager-brazil-at-nuvei-4441367054?refId=WcXTRtyALhxud2A7LehG1w%3D%3D&amp;trackingId=BlscybedpAe9SVy2JE4QXw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enterprise-account-executive-b2b-at-nuvei-4449788756?refId=WcXTRtyALhxud2A7LehG1w%3D%3D&amp;trackingId=0JwlLLBAuV7dCsBZo3BnLQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/developer-platform/paymentfirms</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4690576006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4701943006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4700949006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4691708006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>https://www.fireblocks.com/careers/position?gh_jid=4699832006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sales-director-enterprise-at-fireblocks-4441678999?refId=PUikLmtgyEMIL7fQqVs7QA%3D%3D&amp;trackingId=f6AbQ9gByYEbF4%2FiQX9jUQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-development-representative-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8051996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>https://ripple.com/careers/all-jobs/job/8042882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/business-solutions-architect-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>https://unlimit.com/ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/posts/tags/payment-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/wise-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bvnk/jobs/</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bvnk</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://ch.linkedin.com/company/nevermined</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/openai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/anthropic/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/perplexity-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/scaleai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56:47</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/wise/jobs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L261"/>
+  <dimension ref="A1:L295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-08 08:01:02</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-02 22:51:16</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026-08-08 20:56:47</t>
+          <t>2026-08-08 21:20:40</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -9602,19 +9602,1209 @@
         </is>
       </c>
       <c r="F261" t="n">
+        <v>30</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>45</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424957337?refId=zKlOgViFcJzKHn2JRtzkaQ%3D%3D&amp;trackingId=jSuKAUyJsp%2BNl4YUUxB1Mw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>45</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424958275?refId=zKlOgViFcJzKHn2JRtzkaQ%3D%3D&amp;trackingId=N0FukmYRiWJP7IB6UMCWnw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>45</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424970219?refId=zKlOgViFcJzKHn2JRtzkaQ%3D%3D&amp;trackingId=uTOgLtypw2wWy3qXk%2Bz5PQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>30</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Enterprise Account Manager, Adyen for Platforms</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>55</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/enterprise-account-manager-adyen-for-platforms-at-adyen-4360814131?refId=GySVNDnlN5TZHxoyRnz%2B4Q%3D%3D&amp;trackingId=C9vY%2BCDv7QP1EN7SwY5krA%3D%3D</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>30</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>30</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Director, Commercial Integration &amp; Revenue Performance-Recorded Future Partnership</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
         <v>35</v>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>https://www.reap.global/products/agentic-payments</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>2026-08-08 20:56:47</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-commercial-integration-revenue-performance-recorded-future-partnership-at-mastercard-4451033711?refId=8RR7mzKW6QeuUpo7egzvQw%3D%3D&amp;trackingId=AhoEndr9z80tejGmh25%2FEg%3D%3D</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>30</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>30</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>30</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Senior Manager, Strategic PartnershipsFinancial and Strategic PartnershipsFinancial and Strategic Partnerships•SingaporeAPAC,SingaporeSingapore</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>80</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/c1f4b704-80db-42d3-bd8f-5d8ad972ab5d/senior-manager-strategic-partnerships/</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Senior Manager, Financial Partnerships, APAC (Local Payment Providers)Financial and Strategic PartnershipsFinancial and Strategic Partnerships•SingaporeAPAC,SingaporeSingapore</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>100</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b96cc239-f22f-40ad-aaaf-240849223c15/senior-manager-financial-partnerships-apac-local-payment-providers/</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>30</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Cross-Border Payments</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>70</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/cross-border-payments</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager- Brazil</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>30</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/jobs/view/senior-business-development-manager-brazil-at-nuvei-4441367054?refId=ysevmMlOgn0t5PKfginFDQ%3D%3D&amp;trackingId=%2Fu4wGRjG6nLfNdRMQxWeEQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>30</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Cross-border payments</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>70</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://www.thunes.com/cross-border-payments/</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Cross-Border Payments</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>70</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://www.rapyd.net/solutions/cross-border-payments-solutions/</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>󰄔BusinessCrypto trading and payments for startups and SMBs</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>25</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/business</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>30</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>30</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Online Crypto Payments</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>25</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Online Crypto Payments</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>25</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Online Crypto Payments</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>25</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Online Crypto Payments</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>25</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Online Crypto Payments</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>25</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Business Growth and Partnership ManagerBarcelonaClient Relationsremote</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>30</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/fdd8016f-619e-43dc-80f5-a1f6e507a36b</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Bill PayEfficient cross-border payments.</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>70</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/bill-pay</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>PaymentsAutomated global fiat payouts at scale using stablecoins.</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>25</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/payments</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Bill PayEfficient cross-border payments.</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>70</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/bill-pay</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>PaymentsAutomated global fiat payouts at scale using stablecoins.</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>25</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/payments</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>30</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>JOB-20260808-0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Account Manager jobs121,519 open jobs</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>30</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -10265,7 +11455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10655,8 +11845,35 @@
       <c r="F14" t="n">
         <v>31</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>76</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -10673,7 +11890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1525"/>
+  <dimension ref="A1:E1634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46026,6 +47243,2484 @@
         </is>
       </c>
     </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424957337?refId=zKlOgViFcJzKHn2JRtzkaQ%3D%3D&amp;trackingId=jSuKAUyJsp%2BNl4YUUxB1Mw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424958275?refId=zKlOgViFcJzKHn2JRtzkaQ%3D%3D&amp;trackingId=N0FukmYRiWJP7IB6UMCWnw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-customer-success-manager-at-stripe-4424970219?refId=zKlOgViFcJzKHn2JRtzkaQ%3D%3D&amp;trackingId=uTOgLtypw2wWy3qXk%2Bz5PQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/enterprise-account-manager-adyen-for-platforms-at-adyen-4360814131?refId=GySVNDnlN5TZHxoyRnz%2B4Q%3D%3D&amp;trackingId=C9vY%2BCDv7QP1EN7SwY5krA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-commercial-integration-revenue-performance-recorded-future-partnership-at-mastercard-4451033711?refId=8RR7mzKW6QeuUpo7egzvQw%3D%3D&amp;trackingId=AhoEndr9z80tejGmh25%2FEg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/c1f4b704-80db-42d3-bd8f-5d8ad972ab5d/senior-manager-strategic-partnerships/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/b96cc239-f22f-40ad-aaaf-240849223c15/senior-manager-financial-partnerships-apac-local-payment-providers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0041178d-9b99-4c6e-9ad0-d8399d77559f/senior-manager-financial-partnerships-card-issuing-acquiring-emea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/cross-border-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/how-america-pays-what-1-000-us-shoppers-told-nuvei</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/agentic-commerce-what-it-is-and-how-payments-have-to-change</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/jobs/view/senior-business-development-manager-brazil-at-nuvei-4441367054?refId=ysevmMlOgn0t5PKfginFDQ%3D%3D&amp;trackingId=%2Fu4wGRjG6nLfNdRMQxWeEQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>https://www.thunes.com/cross-border-payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>https://www.rapyd.net/solutions/cross-border-payments-solutions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/developer-platform/paymentfirms</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/fdd8016f-619e-43dc-80f5-a1f6e507a36b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/bill-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/bill-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:20:40</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Job_Dashboard.xlsx
+++ b/output/Job_Dashboard.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L295"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Perplexity</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10801,10 +10801,185 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-08-08 21:20:40</t>
+          <t>2026-08-09 07:56:51</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>JOB-20260809-0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Enterprise Account Manager, Adyen for Platforms</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>55</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/enterprise-account-manager-adyen-for-platforms-at-adyen-4360814131?refId=vTJVpUVVwanE0w%2FfglirYw%3D%3D&amp;trackingId=NIzn1v6xrLN6LOXbAA09Iw%3D%3D</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>JOB-20260809-0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Account Manager, SME &amp; GrowthSalesSales•Kuala LumpurAPAC,Kuala LumpurKuala Lumpur</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>45</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f7b1e3f3-64a1-41d0-9523-af58fb0db835/account-manager-sme-growth/</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>JOB-20260809-0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, SME &amp; Growth (ANZ/SEA)SalesSales•BangaloreAPAC,BangaloreBangalore</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>60</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0793219c-3209-4b48-9df7-e100a13235ed/customer-success-manager-sme-growth-anz-sea/</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>JOB-20260809-0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager- Brazil</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>30</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/jobs/view/senior-business-development-manager-brazil-at-nuvei-4441367054?refId=jeDgpGT93CuAfrMhcZEOfg%3D%3D&amp;trackingId=U2NkWF2FY3QMXQI4db%2BYig%3D%3D</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>JOB-20260809-0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Account Manager- Expansion Representative, US West</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>30</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-manager-expansion-representative-us-west-at-ripple-4392430821?refId=AhiXt0WyPEd3WCHx9Ol%2FOQ%3D%3D&amp;trackingId=RWUXbYcyxpofQ3asgG4hag%3D%3D</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
         <is>
           <t>New</t>
         </is>
@@ -11455,7 +11630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11872,8 +12047,35 @@
       <c r="F15" t="n">
         <v>16</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:52</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>76</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11890,7 +12092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1634"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49721,6 +49923,2708 @@
         </is>
       </c>
     </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>https://stripe.com/careers/listing/account-executive-enterprise-growth/7997146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/enterprise-account-manager-adyen-for-platforms-at-adyen-4360814131?refId=vTJVpUVVwanE0w%2FfglirYw%3D%3D&amp;trackingId=NIzn1v6xrLN6LOXbAA09Iw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/f7b1e3f3-64a1-41d0-9523-af58fb0db835/account-manager-sme-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/job/0793219c-3209-4b48-9df7-e100a13235ed/customer-success-manager-sme-growth-anz-sea/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>https://careers.airwallex.com/blog/airwallex-funding-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/marketplaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/solutions/airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>https://docs.nium.com/travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>https://www.nium.com/cross-border-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/payment-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/issuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/apm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/real-time-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/payment-orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/solutions/crypto-digital-assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/healthcare-payment-solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/crypto-platforms-exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/small-medium-sized-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/business-to-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/online-retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/use-cases/digital-content-subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-and-blackline-partner-to-modernize-the-invoice-to-cash-process-through-embedded-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-completes-first-party-in-agent-payment-with-visa-unveils-merchant-led-agentic-payments-strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/nuvei-to-acquire-payoneer-for-2-75-billion-creating-a-leading-global-platform-for-local-and-cross-border-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/syspro-and-nuvei-partner-to-embed-integrated-payments-into-erp-for-manufacturing-and-distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/how-america-pays-what-1-000-us-shoppers-told-nuvei</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/agentic-commerce-what-it-is-and-how-payments-have-to-change</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>https://www.nuvei.com/posts/why-travel-is-the-hardest-test-for-agentic-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/jobs/view/senior-business-development-manager-brazil-at-nuvei-4441367054?refId=jeDgpGT93CuAfrMhcZEOfg%3D%3D&amp;trackingId=U2NkWF2FY3QMXQI4db%2BYig%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>https://www.rapyd.net/solutions/cross-border-payments-solutions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/business</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/developer-platform/paymentfirms</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/account-manager-expansion-representative-us-west-at-ripple-4392430821?refId=AhiXt0WyPEd3WCHx9Ol%2FOQ%3D%3D&amp;trackingId=RWUXbYcyxpofQ3asgG4hag%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-manager-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>https://www.bvnk.com/self-managed-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>https://bitpay.com/careers/online-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>https://triple-a.io/case-studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>https://www.tazapay.com/payment-methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/80c40d3c-fc55-4641-b6d9-da232aed149b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/296197b1-ce36-43e3-9f58-05084ff3b235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/eb9ef693-37f3-4c33-a0d8-71a84adb0ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/1e5c58cd-f934-4d7b-a44a-4d202d62d07e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/unlimit/fdd8016f-619e-43dc-80f5-a1f6e507a36b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>https://www.baas.unlimit.com/payments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/bill-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/bill-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>https://www.reap.global/products/agentic-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/senior-business-development-manager-banks-in-austin-jid-3921</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>https://wise.jobs/job/customer-success-manager-in-austin-jid-3412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>https://jobs.visa.com/</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/checkout.com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>Thunes</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/thunes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/rapyd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/circle/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>BitPay</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/bitpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>Alchemy Pay</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alchemy-pay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/alchemy-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>Triple-A</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/triple-a-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.straitsx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>StraitsX</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/straitsx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>https://osl.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.osl.com/hk-en/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osl-group/jobs/</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/osl-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>Tazapay</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/tazapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>Unlimit</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.linkedin.com/company/unlimit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>https://www.okx.com/careers</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://www.okx.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/okx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>https://www.gate.io/careers</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.gate.io/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/gateio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/reap-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/meshconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minimax-ai/jobs/</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://sg.linkedin.com/company/minimax-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>https://www.skyfire.xyz/careers</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://skyfire.xyz/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>Skyfire</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/skyfirexyz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>https://nevermined.io/careers</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://nevermined.ai/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>Nevermined</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>429 Client Error: Too Many Requests for url: https://www.linkedin.com/company/nevermined/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:56:51</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>SCAN_FAILED</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c